--- a/research/traditional_assets/database/data/italy/italy_homebuilding.xlsx
+++ b/research/traditional_assets/database/data/italy/italy_homebuilding.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1159309773873305</v>
+        <v>0.1156869430416009</v>
       </c>
       <c r="C2">
-        <v>233.5163587265496</v>
+        <v>231.8749871592465</v>
       </c>
       <c r="D2">
-        <v>218.1163587265496</v>
+        <v>218.8779871592465</v>
       </c>
       <c r="E2">
-        <v>-125.2</v>
+        <v>-122.797</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.403</v>
       </c>
       <c r="G2">
         <v>15.4</v>
@@ -1451,28 +1451,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1208709</v>
       </c>
       <c r="N2">
-        <v>23.91333333333333</v>
+        <v>23.79246243333333</v>
       </c>
       <c r="O2">
-        <v>5.7392</v>
+        <v>5.710190984</v>
       </c>
       <c r="P2">
-        <v>18.17413333333333</v>
+        <v>18.08227144933333</v>
       </c>
       <c r="Q2">
-        <v>19.59413333333333</v>
+        <v>19.50227144933334</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1159309773873305</v>
+        <v>0.1164693566076777</v>
       </c>
       <c r="T2">
-        <v>0.9653793013859414</v>
+        <v>0.9727902940026416</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>197.8419398989611</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1156869430416009</v>
+        <v>0.1154429086958713</v>
       </c>
       <c r="C3">
-        <v>231.8749871592465</v>
+        <v>230.2389532063466</v>
       </c>
       <c r="D3">
-        <v>218.8779871592465</v>
+        <v>219.6449532063466</v>
       </c>
       <c r="E3">
-        <v>-122.797</v>
+        <v>-120.394</v>
       </c>
       <c r="F3">
-        <v>2.403</v>
+        <v>4.806</v>
       </c>
       <c r="G3">
         <v>15.4</v>
@@ -1533,28 +1533,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M3">
-        <v>0.1208709</v>
+        <v>0.2417418</v>
       </c>
       <c r="N3">
-        <v>23.79246243333333</v>
+        <v>23.67159153333333</v>
       </c>
       <c r="O3">
-        <v>5.710190984</v>
+        <v>5.681181968</v>
       </c>
       <c r="P3">
-        <v>18.08227144933333</v>
+        <v>17.99040956533333</v>
       </c>
       <c r="Q3">
-        <v>19.50227144933334</v>
+        <v>19.41040956533333</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1164693566076777</v>
+        <v>0.1170187231590523</v>
       </c>
       <c r="T3">
-        <v>0.9727902940026416</v>
+        <v>0.9803525313666213</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>197.8419398989611</v>
+        <v>98.92096994948055</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1154429086958713</v>
+        <v>0.1151988743501417</v>
       </c>
       <c r="C4">
-        <v>230.2389532063466</v>
+        <v>228.6083131754447</v>
       </c>
       <c r="D4">
-        <v>219.6449532063466</v>
+        <v>220.4173131754447</v>
       </c>
       <c r="E4">
-        <v>-120.394</v>
+        <v>-117.991</v>
       </c>
       <c r="F4">
-        <v>4.806</v>
+        <v>7.209</v>
       </c>
       <c r="G4">
         <v>15.4</v>
@@ -1615,28 +1615,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M4">
-        <v>0.2417418</v>
+        <v>0.3626127</v>
       </c>
       <c r="N4">
-        <v>23.67159153333333</v>
+        <v>23.55072063333333</v>
       </c>
       <c r="O4">
-        <v>5.681181968</v>
+        <v>5.652172952</v>
       </c>
       <c r="P4">
-        <v>17.99040956533333</v>
+        <v>17.89854768133333</v>
       </c>
       <c r="Q4">
-        <v>19.41040956533333</v>
+        <v>19.31854768133334</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1170187231590523</v>
+        <v>0.1175794168558162</v>
       </c>
       <c r="T4">
-        <v>0.9803525313666213</v>
+        <v>0.9880706911504771</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>98.92096994948055</v>
+        <v>65.9473132996537</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1151988743501417</v>
+        <v>0.1149548400044121</v>
       </c>
       <c r="C5">
-        <v>228.6083131754447</v>
+        <v>226.9831241689314</v>
       </c>
       <c r="D5">
-        <v>220.4173131754447</v>
+        <v>221.1951241689314</v>
       </c>
       <c r="E5">
-        <v>-117.991</v>
+        <v>-115.588</v>
       </c>
       <c r="F5">
-        <v>7.209</v>
+        <v>9.612</v>
       </c>
       <c r="G5">
         <v>15.4</v>
@@ -1697,28 +1697,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M5">
-        <v>0.3626127</v>
+        <v>0.4834836</v>
       </c>
       <c r="N5">
-        <v>23.55072063333333</v>
+        <v>23.42984973333333</v>
       </c>
       <c r="O5">
-        <v>5.652172952</v>
+        <v>5.623163936</v>
       </c>
       <c r="P5">
-        <v>17.89854768133333</v>
+        <v>17.80668579733333</v>
       </c>
       <c r="Q5">
-        <v>19.31854768133334</v>
+        <v>19.22668579733333</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1175794168558162</v>
+        <v>0.1181517916712626</v>
       </c>
       <c r="T5">
-        <v>0.9880706911504771</v>
+        <v>0.9959496459298296</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>65.9473132996537</v>
+        <v>49.46048497474028</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1149548400044121</v>
+        <v>0.1147108056586825</v>
       </c>
       <c r="C6">
-        <v>226.9831241689314</v>
+        <v>225.3634440980656</v>
       </c>
       <c r="D6">
-        <v>221.1951241689314</v>
+        <v>221.9784440980656</v>
       </c>
       <c r="E6">
-        <v>-115.588</v>
+        <v>-113.185</v>
       </c>
       <c r="F6">
-        <v>9.612</v>
+        <v>12.015</v>
       </c>
       <c r="G6">
         <v>15.4</v>
@@ -1779,28 +1779,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M6">
-        <v>0.4834836</v>
+        <v>0.6043545</v>
       </c>
       <c r="N6">
-        <v>23.42984973333333</v>
+        <v>23.30897883333333</v>
       </c>
       <c r="O6">
-        <v>5.623163936</v>
+        <v>5.59415492</v>
       </c>
       <c r="P6">
-        <v>17.80668579733333</v>
+        <v>17.71482391333333</v>
       </c>
       <c r="Q6">
-        <v>19.22668579733333</v>
+        <v>19.13482391333334</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1181517916712626</v>
+        <v>0.1187362164828237</v>
       </c>
       <c r="T6">
-        <v>0.9959496459298296</v>
+        <v>1.003994473441379</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>49.46048497474028</v>
+        <v>39.56838797979221</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1147108056586825</v>
+        <v>0.1144667713129529</v>
       </c>
       <c r="C7">
-        <v>225.3634440980656</v>
+        <v>223.7493316973479</v>
       </c>
       <c r="D7">
-        <v>221.9784440980656</v>
+        <v>222.7673316973479</v>
       </c>
       <c r="E7">
-        <v>-113.185</v>
+        <v>-110.782</v>
       </c>
       <c r="F7">
-        <v>12.015</v>
+        <v>14.418</v>
       </c>
       <c r="G7">
         <v>15.4</v>
@@ -1861,28 +1861,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M7">
-        <v>0.6043545</v>
+        <v>0.7252254</v>
       </c>
       <c r="N7">
-        <v>23.30897883333333</v>
+        <v>23.18810793333333</v>
       </c>
       <c r="O7">
-        <v>5.59415492</v>
+        <v>5.565145904</v>
       </c>
       <c r="P7">
-        <v>17.71482391333333</v>
+        <v>17.62296202933333</v>
       </c>
       <c r="Q7">
-        <v>19.13482391333334</v>
+        <v>19.04296202933333</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1187362164828237</v>
+        <v>0.1193330758648435</v>
       </c>
       <c r="T7">
-        <v>1.003994473441379</v>
+        <v>1.012210467495728</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>39.56838797979221</v>
+        <v>32.97365664982685</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1144667713129529</v>
+        <v>0.1142227369672233</v>
       </c>
       <c r="C8">
-        <v>223.7493316973479</v>
+        <v>222.1408465392012</v>
       </c>
       <c r="D8">
-        <v>222.7673316973479</v>
+        <v>223.5618465392012</v>
       </c>
       <c r="E8">
-        <v>-110.782</v>
+        <v>-108.379</v>
       </c>
       <c r="F8">
-        <v>14.418</v>
+        <v>16.821</v>
       </c>
       <c r="G8">
         <v>15.4</v>
@@ -1943,28 +1943,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M8">
-        <v>0.7252253999999999</v>
+        <v>0.8460962999999998</v>
       </c>
       <c r="N8">
-        <v>23.18810793333333</v>
+        <v>23.06723703333333</v>
       </c>
       <c r="O8">
-        <v>5.565145904</v>
+        <v>5.536136888</v>
       </c>
       <c r="P8">
-        <v>17.62296202933333</v>
+        <v>17.53110014533333</v>
       </c>
       <c r="Q8">
-        <v>19.04296202933333</v>
+        <v>18.95110014533333</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1193330758648435</v>
+        <v>0.1199427709324982</v>
       </c>
       <c r="T8">
-        <v>1.012210467495728</v>
+        <v>1.020603149594255</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>32.97365664982685</v>
+        <v>28.26313427128016</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1142227369672233</v>
+        <v>0.1139787026214937</v>
       </c>
       <c r="C9">
-        <v>222.1408465392013</v>
+        <v>220.538049048967</v>
       </c>
       <c r="D9">
-        <v>223.5618465392013</v>
+        <v>224.362049048967</v>
       </c>
       <c r="E9">
-        <v>-108.379</v>
+        <v>-105.976</v>
       </c>
       <c r="F9">
-        <v>16.821</v>
+        <v>19.224</v>
       </c>
       <c r="G9">
         <v>15.4</v>
@@ -2025,28 +2025,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M9">
-        <v>0.8460963</v>
+        <v>0.9669671999999999</v>
       </c>
       <c r="N9">
-        <v>23.06723703333333</v>
+        <v>22.94636613333333</v>
       </c>
       <c r="O9">
-        <v>5.536136888</v>
+        <v>5.507127872</v>
       </c>
       <c r="P9">
-        <v>17.53110014533333</v>
+        <v>17.43923826133334</v>
       </c>
       <c r="Q9">
-        <v>18.95110014533333</v>
+        <v>18.85923826133334</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1199427709324982</v>
+        <v>0.120565720240754</v>
       </c>
       <c r="T9">
-        <v>1.020603149594255</v>
+        <v>1.029178281303621</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>28.26313427128015</v>
+        <v>24.73024248737014</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1139787026214937</v>
+        <v>0.1137346682757641</v>
       </c>
       <c r="C10">
-        <v>220.538049048967</v>
+        <v>218.9410005202241</v>
       </c>
       <c r="D10">
-        <v>224.362049048967</v>
+        <v>225.1680005202241</v>
       </c>
       <c r="E10">
-        <v>-105.976</v>
+        <v>-103.573</v>
       </c>
       <c r="F10">
-        <v>19.224</v>
+        <v>21.627</v>
       </c>
       <c r="G10">
         <v>15.4</v>
@@ -2107,28 +2107,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M10">
-        <v>0.9669671999999999</v>
+        <v>1.0878381</v>
       </c>
       <c r="N10">
-        <v>22.94636613333333</v>
+        <v>22.82549523333333</v>
       </c>
       <c r="O10">
-        <v>5.507127872</v>
+        <v>5.478118856</v>
       </c>
       <c r="P10">
-        <v>17.43923826133334</v>
+        <v>17.34737637733333</v>
       </c>
       <c r="Q10">
-        <v>18.85923826133334</v>
+        <v>18.76737637733333</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.120565720240754</v>
+        <v>0.1212023607425979</v>
       </c>
       <c r="T10">
-        <v>1.029178281303621</v>
+        <v>1.037941877446159</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>24.73024248737014</v>
+        <v>21.98243776655123</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1137346682757641</v>
+        <v>0.1134906339300345</v>
       </c>
       <c r="C11">
-        <v>218.9410005202241</v>
+        <v>217.3497631304397</v>
       </c>
       <c r="D11">
-        <v>225.1680005202241</v>
+        <v>225.9797631304397</v>
       </c>
       <c r="E11">
-        <v>-103.573</v>
+        <v>-101.17</v>
       </c>
       <c r="F11">
-        <v>21.627</v>
+        <v>24.03</v>
       </c>
       <c r="G11">
         <v>15.4</v>
@@ -2189,28 +2189,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M11">
-        <v>1.0878381</v>
+        <v>1.208709</v>
       </c>
       <c r="N11">
-        <v>22.82549523333333</v>
+        <v>22.70462433333334</v>
       </c>
       <c r="O11">
-        <v>5.478118856</v>
+        <v>5.44910984</v>
       </c>
       <c r="P11">
-        <v>17.34737637733333</v>
+        <v>17.25551449333334</v>
       </c>
       <c r="Q11">
-        <v>18.76737637733333</v>
+        <v>18.67551449333334</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1212023607425979</v>
+        <v>0.1218531488111495</v>
       </c>
       <c r="T11">
-        <v>1.037941877446159</v>
+        <v>1.046900220169643</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.98243776655123</v>
+        <v>19.78419398989611</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1134906339300345</v>
+        <v>0.1132465995843049</v>
       </c>
       <c r="C12">
-        <v>217.3497631304397</v>
+        <v>215.7643999569596</v>
       </c>
       <c r="D12">
-        <v>225.9797631304397</v>
+        <v>226.7973999569596</v>
       </c>
       <c r="E12">
-        <v>-101.17</v>
+        <v>-98.767</v>
       </c>
       <c r="F12">
-        <v>24.03</v>
+        <v>26.433</v>
       </c>
       <c r="G12">
         <v>15.4</v>
@@ -2271,28 +2271,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M12">
-        <v>1.208709</v>
+        <v>1.3295799</v>
       </c>
       <c r="N12">
-        <v>22.70462433333334</v>
+        <v>22.58375343333334</v>
       </c>
       <c r="O12">
-        <v>5.44910984</v>
+        <v>5.420100824</v>
       </c>
       <c r="P12">
-        <v>17.25551449333334</v>
+        <v>17.16365260933333</v>
       </c>
       <c r="Q12">
-        <v>18.67551449333334</v>
+        <v>18.58365260933333</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1218531488111495</v>
+        <v>0.1225185613306797</v>
       </c>
       <c r="T12">
-        <v>1.046900220169643</v>
+        <v>1.056059873965565</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.78419398989611</v>
+        <v>17.98563089990555</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1132465995843049</v>
+        <v>0.1130025652385753</v>
       </c>
       <c r="C13">
-        <v>215.7643999569596</v>
+        <v>214.1849749933468</v>
       </c>
       <c r="D13">
-        <v>226.7973999569596</v>
+        <v>227.6209749933468</v>
       </c>
       <c r="E13">
-        <v>-98.767</v>
+        <v>-96.364</v>
       </c>
       <c r="F13">
-        <v>26.433</v>
+        <v>28.836</v>
       </c>
       <c r="G13">
         <v>15.4</v>
@@ -2353,28 +2353,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M13">
-        <v>1.3295799</v>
+        <v>1.4504508</v>
       </c>
       <c r="N13">
-        <v>22.58375343333334</v>
+        <v>22.46288253333334</v>
       </c>
       <c r="O13">
-        <v>5.420100824</v>
+        <v>5.391091808000001</v>
       </c>
       <c r="P13">
-        <v>17.16365260933333</v>
+        <v>17.07179072533334</v>
       </c>
       <c r="Q13">
-        <v>18.58365260933333</v>
+        <v>18.49179072533334</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1225185613306797</v>
+        <v>0.1231990968620174</v>
       </c>
       <c r="T13">
-        <v>1.056059873965565</v>
+        <v>1.065427701711393</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.98563089990555</v>
+        <v>16.48682832491343</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1130025652385753</v>
+        <v>0.1127585308928457</v>
       </c>
       <c r="C14">
-        <v>214.1849749933468</v>
+        <v>212.6115531660777</v>
       </c>
       <c r="D14">
-        <v>227.6209749933468</v>
+        <v>228.4505531660777</v>
       </c>
       <c r="E14">
-        <v>-96.364</v>
+        <v>-93.961</v>
       </c>
       <c r="F14">
-        <v>28.836</v>
+        <v>31.239</v>
       </c>
       <c r="G14">
         <v>15.4</v>
@@ -2435,28 +2435,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M14">
-        <v>1.4504508</v>
+        <v>1.5713217</v>
       </c>
       <c r="N14">
-        <v>22.46288253333334</v>
+        <v>22.34201163333334</v>
       </c>
       <c r="O14">
-        <v>5.391091808000001</v>
+        <v>5.362082792000001</v>
       </c>
       <c r="P14">
-        <v>17.07179072533334</v>
+        <v>16.97992884133333</v>
       </c>
       <c r="Q14">
-        <v>18.49179072533334</v>
+        <v>18.39992884133333</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1231990968620174</v>
+        <v>0.1238952768883284</v>
       </c>
       <c r="T14">
-        <v>1.065427701711393</v>
+        <v>1.075010881819195</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.48682832491343</v>
+        <v>15.21861076145854</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1127585308928457</v>
+        <v>0.1125144965471161</v>
       </c>
       <c r="C15">
-        <v>212.6115531660777</v>
+        <v>211.0442003516046</v>
       </c>
       <c r="D15">
-        <v>228.4505531660777</v>
+        <v>229.2862003516046</v>
       </c>
       <c r="E15">
-        <v>-93.961</v>
+        <v>-91.55799999999999</v>
       </c>
       <c r="F15">
-        <v>31.239</v>
+        <v>33.642</v>
       </c>
       <c r="G15">
         <v>15.4</v>
@@ -2517,28 +2517,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M15">
-        <v>1.5713217</v>
+        <v>1.6921926</v>
       </c>
       <c r="N15">
-        <v>22.34201163333334</v>
+        <v>22.22114073333334</v>
       </c>
       <c r="O15">
-        <v>5.362082792000001</v>
+        <v>5.333073776</v>
       </c>
       <c r="P15">
-        <v>16.97992884133333</v>
+        <v>16.88806695733334</v>
       </c>
       <c r="Q15">
-        <v>18.39992884133333</v>
+        <v>18.30806695733334</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1238952768883284</v>
+        <v>0.1246076471478095</v>
       </c>
       <c r="T15">
-        <v>1.075010881819195</v>
+        <v>1.084816926580667</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.21861076145854</v>
+        <v>14.13156713564008</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1125144965471161</v>
+        <v>0.1122704622013866</v>
       </c>
       <c r="C16">
-        <v>211.0442003516046</v>
+        <v>209.4829833937942</v>
       </c>
       <c r="D16">
-        <v>229.2862003516046</v>
+        <v>230.1279833937942</v>
       </c>
       <c r="E16">
-        <v>-91.55799999999999</v>
+        <v>-89.155</v>
       </c>
       <c r="F16">
-        <v>33.642</v>
+        <v>36.04500000000001</v>
       </c>
       <c r="G16">
         <v>15.4</v>
@@ -2599,28 +2599,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M16">
-        <v>1.6921926</v>
+        <v>1.8130635</v>
       </c>
       <c r="N16">
-        <v>22.22114073333334</v>
+        <v>22.10026983333333</v>
       </c>
       <c r="O16">
-        <v>5.333073776</v>
+        <v>5.304064759999999</v>
       </c>
       <c r="P16">
-        <v>16.88806695733334</v>
+        <v>16.79620507333333</v>
       </c>
       <c r="Q16">
-        <v>18.30806695733334</v>
+        <v>18.21620507333333</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1246076471478095</v>
+        <v>0.1253367790604548</v>
       </c>
       <c r="T16">
-        <v>1.084816926580667</v>
+        <v>1.094853701807115</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.13156713564008</v>
+        <v>13.18946265993073</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1122704622013866</v>
+        <v>0.112208827855657</v>
       </c>
       <c r="C17">
-        <v>209.4829833937942</v>
+        <v>207.2935662584304</v>
       </c>
       <c r="D17">
-        <v>230.1279833937942</v>
+        <v>230.3415662584304</v>
       </c>
       <c r="E17">
-        <v>-89.155</v>
+        <v>-86.75200000000001</v>
       </c>
       <c r="F17">
-        <v>36.045</v>
+        <v>38.448</v>
       </c>
       <c r="G17">
         <v>15.4</v>
@@ -2681,45 +2681,45 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M17">
-        <v>1.8130635</v>
+        <v>1.9916064</v>
       </c>
       <c r="N17">
-        <v>22.10026983333334</v>
+        <v>21.92172693333334</v>
       </c>
       <c r="O17">
-        <v>5.30406476</v>
+        <v>5.261214464</v>
       </c>
       <c r="P17">
-        <v>16.79620507333334</v>
+        <v>16.66051246933333</v>
       </c>
       <c r="Q17">
-        <v>18.21620507333333</v>
+        <v>18.08051246933334</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1253367790604548</v>
+        <v>0.1260832712567345</v>
       </c>
       <c r="T17">
-        <v>1.094853701807115</v>
+        <v>1.105129447872287</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.24</v>
       </c>
       <c r="W17">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>13.18946265993074</v>
+        <v>12.0070578872077</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.112208827855657</v>
+        <v>0.1119761935099274</v>
       </c>
       <c r="C18">
-        <v>207.2935662584304</v>
+        <v>205.7003039710237</v>
       </c>
       <c r="D18">
-        <v>230.3415662584304</v>
+        <v>231.1513039710237</v>
       </c>
       <c r="E18">
-        <v>-86.75200000000001</v>
+        <v>-84.34899999999999</v>
       </c>
       <c r="F18">
-        <v>38.448</v>
+        <v>40.85100000000001</v>
       </c>
       <c r="G18">
         <v>15.4</v>
@@ -2763,28 +2763,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M18">
-        <v>1.9916064</v>
+        <v>2.1160818</v>
       </c>
       <c r="N18">
-        <v>21.92172693333334</v>
+        <v>21.79725153333333</v>
       </c>
       <c r="O18">
-        <v>5.261214464</v>
+        <v>5.231340368</v>
       </c>
       <c r="P18">
-        <v>16.66051246933333</v>
+        <v>16.56591116533333</v>
       </c>
       <c r="Q18">
-        <v>18.08051246933334</v>
+        <v>17.98591116533333</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1260832712567345</v>
+        <v>0.12684775121678</v>
       </c>
       <c r="T18">
-        <v>1.105129447872287</v>
+        <v>1.11565280227638</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>12.0070578872077</v>
+        <v>11.30076036443078</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1119761935099274</v>
+        <v>0.1117435591641978</v>
       </c>
       <c r="C19">
-        <v>205.7003039710237</v>
+        <v>204.1127548360573</v>
       </c>
       <c r="D19">
-        <v>231.1513039710237</v>
+        <v>231.9667548360573</v>
       </c>
       <c r="E19">
-        <v>-84.34899999999999</v>
+        <v>-81.946</v>
       </c>
       <c r="F19">
-        <v>40.85100000000001</v>
+        <v>43.254</v>
       </c>
       <c r="G19">
         <v>15.4</v>
@@ -2845,28 +2845,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M19">
-        <v>2.1160818</v>
+        <v>2.2405572</v>
       </c>
       <c r="N19">
-        <v>21.79725153333333</v>
+        <v>21.67277613333333</v>
       </c>
       <c r="O19">
-        <v>5.231340368</v>
+        <v>5.201466271999999</v>
       </c>
       <c r="P19">
-        <v>16.56591116533333</v>
+        <v>16.47130986133333</v>
       </c>
       <c r="Q19">
-        <v>17.98591116533333</v>
+        <v>17.89130986133333</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.12684775121678</v>
+        <v>0.1276308770295095</v>
       </c>
       <c r="T19">
-        <v>1.11565280227638</v>
+        <v>1.12643282386106</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.30076036443078</v>
+        <v>10.67294034418462</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1117435591641978</v>
+        <v>0.1115109248184682</v>
       </c>
       <c r="C20">
-        <v>204.1127548360574</v>
+        <v>202.5309795318196</v>
       </c>
       <c r="D20">
-        <v>231.9667548360574</v>
+        <v>232.7879795318196</v>
       </c>
       <c r="E20">
-        <v>-81.946</v>
+        <v>-79.54300000000001</v>
       </c>
       <c r="F20">
-        <v>43.254</v>
+        <v>45.657</v>
       </c>
       <c r="G20">
         <v>15.4</v>
@@ -2927,28 +2927,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M20">
-        <v>2.2405572</v>
+        <v>2.3650326</v>
       </c>
       <c r="N20">
-        <v>21.67277613333333</v>
+        <v>21.54830073333333</v>
       </c>
       <c r="O20">
-        <v>5.201466271999999</v>
+        <v>5.171592176</v>
       </c>
       <c r="P20">
-        <v>16.47130986133333</v>
+        <v>16.37670855733333</v>
       </c>
       <c r="Q20">
-        <v>17.89130986133333</v>
+        <v>17.79670855733333</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1276308770295095</v>
+        <v>0.1284333392820595</v>
       </c>
       <c r="T20">
-        <v>1.126432823861059</v>
+        <v>1.1374790188182</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.67294034418462</v>
+        <v>10.11120664185912</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1115109248184682</v>
+        <v>0.1115366904727386</v>
       </c>
       <c r="C21">
-        <v>202.5309795318196</v>
+        <v>200.0367377221729</v>
       </c>
       <c r="D21">
-        <v>232.7879795318196</v>
+        <v>232.6967377221729</v>
       </c>
       <c r="E21">
-        <v>-79.54300000000001</v>
+        <v>-77.14</v>
       </c>
       <c r="F21">
-        <v>45.657</v>
+        <v>48.06</v>
       </c>
       <c r="G21">
         <v>15.4</v>
@@ -3009,45 +3009,45 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M21">
-        <v>2.3650326</v>
+        <v>2.57121</v>
       </c>
       <c r="N21">
-        <v>21.54830073333333</v>
+        <v>21.34212333333333</v>
       </c>
       <c r="O21">
-        <v>5.171592176</v>
+        <v>5.1221096</v>
       </c>
       <c r="P21">
-        <v>16.37670855733333</v>
+        <v>16.22001373333333</v>
       </c>
       <c r="Q21">
-        <v>17.79670855733333</v>
+        <v>17.64001373333333</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1284333392820595</v>
+        <v>0.1292558630909232</v>
       </c>
       <c r="T21">
-        <v>1.1374790188182</v>
+        <v>1.14880136864927</v>
       </c>
       <c r="U21">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V21">
         <v>0.24</v>
       </c>
       <c r="W21">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>10.11120664185912</v>
+        <v>9.300420165343683</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1115366904727386</v>
+        <v>0.111316976127009</v>
       </c>
       <c r="C22">
-        <v>200.0367377221729</v>
+        <v>198.4140974778326</v>
       </c>
       <c r="D22">
-        <v>232.6967377221729</v>
+        <v>233.4770974778326</v>
       </c>
       <c r="E22">
-        <v>-77.14</v>
+        <v>-74.73699999999999</v>
       </c>
       <c r="F22">
-        <v>48.06</v>
+        <v>50.46300000000001</v>
       </c>
       <c r="G22">
         <v>15.4</v>
@@ -3091,28 +3091,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M22">
-        <v>2.57121</v>
+        <v>2.699770500000001</v>
       </c>
       <c r="N22">
-        <v>21.34212333333333</v>
+        <v>21.21356283333333</v>
       </c>
       <c r="O22">
-        <v>5.1221096</v>
+        <v>5.09125508</v>
       </c>
       <c r="P22">
-        <v>16.22001373333333</v>
+        <v>16.12230775333333</v>
       </c>
       <c r="Q22">
-        <v>17.64001373333333</v>
+        <v>17.54230775333333</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1292558630909232</v>
+        <v>0.1300992102873532</v>
       </c>
       <c r="T22">
-        <v>1.14880136864927</v>
+        <v>1.160410360248215</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.300420165343683</v>
+        <v>8.857543014613032</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.111316976127009</v>
+        <v>0.1110972617812794</v>
       </c>
       <c r="C23">
-        <v>198.4140974778326</v>
+        <v>196.7967087931587</v>
       </c>
       <c r="D23">
-        <v>233.4770974778326</v>
+        <v>234.2627087931587</v>
       </c>
       <c r="E23">
-        <v>-74.73699999999999</v>
+        <v>-72.334</v>
       </c>
       <c r="F23">
-        <v>50.463</v>
+        <v>52.866</v>
       </c>
       <c r="G23">
         <v>15.4</v>
@@ -3173,28 +3173,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M23">
-        <v>2.6997705</v>
+        <v>2.828331</v>
       </c>
       <c r="N23">
-        <v>21.21356283333333</v>
+        <v>21.08500233333334</v>
       </c>
       <c r="O23">
-        <v>5.09125508</v>
+        <v>5.060400560000001</v>
       </c>
       <c r="P23">
-        <v>16.12230775333333</v>
+        <v>16.02460177333333</v>
       </c>
       <c r="Q23">
-        <v>17.54230775333333</v>
+        <v>17.44460177333333</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1300992102873532</v>
+        <v>0.130964181770871</v>
       </c>
       <c r="T23">
-        <v>1.160410360248215</v>
+        <v>1.172317018298415</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.857543014613032</v>
+        <v>8.454927423039713</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1110972617812794</v>
+        <v>0.1108775474355498</v>
       </c>
       <c r="C24">
-        <v>196.7967087931587</v>
+        <v>195.1846248589847</v>
       </c>
       <c r="D24">
-        <v>234.2627087931587</v>
+        <v>235.0536248589847</v>
       </c>
       <c r="E24">
-        <v>-72.334</v>
+        <v>-69.931</v>
       </c>
       <c r="F24">
-        <v>52.866</v>
+        <v>55.26900000000001</v>
       </c>
       <c r="G24">
         <v>15.4</v>
@@ -3255,28 +3255,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M24">
-        <v>2.828331</v>
+        <v>2.9568915</v>
       </c>
       <c r="N24">
-        <v>21.08500233333334</v>
+        <v>20.95644183333333</v>
       </c>
       <c r="O24">
-        <v>5.060400560000001</v>
+        <v>5.02954604</v>
       </c>
       <c r="P24">
-        <v>16.02460177333333</v>
+        <v>15.92689579333333</v>
       </c>
       <c r="Q24">
-        <v>17.44460177333333</v>
+        <v>17.34689579333333</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.130964181770871</v>
+        <v>0.1318516200461686</v>
       </c>
       <c r="T24">
-        <v>1.172317018298415</v>
+        <v>1.184532940194075</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.454927423039713</v>
+        <v>8.087321882907551</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1108775474355498</v>
+        <v>0.1106578330898202</v>
       </c>
       <c r="C25">
-        <v>195.1846248589847</v>
+        <v>193.5778995869076</v>
       </c>
       <c r="D25">
-        <v>235.0536248589847</v>
+        <v>235.8498995869076</v>
       </c>
       <c r="E25">
-        <v>-69.931</v>
+        <v>-67.52799999999999</v>
       </c>
       <c r="F25">
-        <v>55.26900000000001</v>
+        <v>57.672</v>
       </c>
       <c r="G25">
         <v>15.4</v>
@@ -3337,28 +3337,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M25">
-        <v>2.9568915</v>
+        <v>3.085452</v>
       </c>
       <c r="N25">
-        <v>20.95644183333333</v>
+        <v>20.82788133333333</v>
       </c>
       <c r="O25">
-        <v>5.02954604</v>
+        <v>4.99869152</v>
       </c>
       <c r="P25">
-        <v>15.92689579333333</v>
+        <v>15.82918981333333</v>
       </c>
       <c r="Q25">
-        <v>17.34689579333333</v>
+        <v>17.24918981333333</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1318516200461686</v>
+        <v>0.1327624119602898</v>
       </c>
       <c r="T25">
-        <v>1.184532940194075</v>
+        <v>1.197070333718567</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.087321882907551</v>
+        <v>7.750350137786403</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1106578330898202</v>
+        <v>0.1105901187440906</v>
       </c>
       <c r="C26">
-        <v>193.5778995869076</v>
+        <v>191.4213942986089</v>
       </c>
       <c r="D26">
-        <v>235.8498995869076</v>
+        <v>236.0963942986089</v>
       </c>
       <c r="E26">
-        <v>-67.52800000000001</v>
+        <v>-65.125</v>
       </c>
       <c r="F26">
-        <v>57.672</v>
+        <v>60.075</v>
       </c>
       <c r="G26">
         <v>15.4</v>
@@ -3419,45 +3419,45 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M26">
-        <v>3.085452</v>
+        <v>3.2620725</v>
       </c>
       <c r="N26">
-        <v>20.82788133333333</v>
+        <v>20.65126083333333</v>
       </c>
       <c r="O26">
-        <v>4.99869152</v>
+        <v>4.9563026</v>
       </c>
       <c r="P26">
-        <v>15.82918981333333</v>
+        <v>15.69495823333333</v>
       </c>
       <c r="Q26">
-        <v>17.24918981333333</v>
+        <v>17.11495823333333</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1327624119602898</v>
+        <v>0.1336974916587875</v>
       </c>
       <c r="T26">
-        <v>1.197070333718567</v>
+        <v>1.209942057737047</v>
       </c>
       <c r="U26">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V26">
         <v>0.24</v>
       </c>
       <c r="W26">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>7.750350137786405</v>
+        <v>7.330717920381392</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1105901187440906</v>
+        <v>0.110376484398361</v>
       </c>
       <c r="C27">
-        <v>191.4213942986089</v>
+        <v>189.7994572380831</v>
       </c>
       <c r="D27">
-        <v>236.0963942986089</v>
+        <v>236.8774572380831</v>
       </c>
       <c r="E27">
-        <v>-65.125</v>
+        <v>-62.72199999999999</v>
       </c>
       <c r="F27">
-        <v>60.075</v>
+        <v>62.47800000000001</v>
       </c>
       <c r="G27">
         <v>15.4</v>
@@ -3501,28 +3501,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M27">
-        <v>3.2620725</v>
+        <v>3.3925554</v>
       </c>
       <c r="N27">
-        <v>20.65126083333333</v>
+        <v>20.52077793333333</v>
       </c>
       <c r="O27">
-        <v>4.9563026</v>
+        <v>4.924986704</v>
       </c>
       <c r="P27">
-        <v>15.69495823333333</v>
+        <v>15.59579122933333</v>
       </c>
       <c r="Q27">
-        <v>17.11495823333333</v>
+        <v>17.01579122933333</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1336974916587875</v>
+        <v>0.134657843781569</v>
       </c>
       <c r="T27">
-        <v>1.209942057737047</v>
+        <v>1.223161666188458</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.330717920381392</v>
+        <v>7.048767231135955</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.110376484398361</v>
+        <v>0.1101628500526314</v>
       </c>
       <c r="C28">
-        <v>189.7994572380831</v>
+        <v>188.1827052142645</v>
       </c>
       <c r="D28">
-        <v>236.8774572380831</v>
+        <v>237.6637052142645</v>
       </c>
       <c r="E28">
-        <v>-62.72199999999999</v>
+        <v>-60.31899999999999</v>
       </c>
       <c r="F28">
-        <v>62.47800000000001</v>
+        <v>64.88100000000001</v>
       </c>
       <c r="G28">
         <v>15.4</v>
@@ -3583,28 +3583,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M28">
-        <v>3.3925554</v>
+        <v>3.523038300000001</v>
       </c>
       <c r="N28">
-        <v>20.52077793333333</v>
+        <v>20.39029503333333</v>
       </c>
       <c r="O28">
-        <v>4.924986704</v>
+        <v>4.893670808</v>
       </c>
       <c r="P28">
-        <v>15.59579122933333</v>
+        <v>15.49662422533333</v>
       </c>
       <c r="Q28">
-        <v>17.01579122933333</v>
+        <v>16.91662422533334</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.134657843781569</v>
+        <v>0.1356445069214129</v>
       </c>
       <c r="T28">
-        <v>1.223161666188458</v>
+        <v>1.236743455693332</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.048767231135955</v>
+        <v>6.787701778130919</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1101628500526314</v>
+        <v>0.1099492157069018</v>
       </c>
       <c r="C29">
-        <v>188.1827052142645</v>
+        <v>186.5711900299029</v>
       </c>
       <c r="D29">
-        <v>237.6637052142645</v>
+        <v>238.4551900299029</v>
       </c>
       <c r="E29">
-        <v>-60.31899999999999</v>
+        <v>-57.916</v>
       </c>
       <c r="F29">
-        <v>64.88100000000001</v>
+        <v>67.28400000000001</v>
       </c>
       <c r="G29">
         <v>15.4</v>
@@ -3665,28 +3665,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M29">
-        <v>3.523038300000001</v>
+        <v>3.653521200000001</v>
       </c>
       <c r="N29">
-        <v>20.39029503333333</v>
+        <v>20.25981213333333</v>
       </c>
       <c r="O29">
-        <v>4.893670808</v>
+        <v>4.862354912</v>
       </c>
       <c r="P29">
-        <v>15.49662422533333</v>
+        <v>15.39745722133333</v>
       </c>
       <c r="Q29">
-        <v>16.91662422533334</v>
+        <v>16.81745722133333</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1356445069214129</v>
+        <v>0.136658577370697</v>
       </c>
       <c r="T29">
-        <v>1.236743455693332</v>
+        <v>1.250702517128897</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.787701778130919</v>
+        <v>6.545283857483386</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1099492157069018</v>
+        <v>0.1097355813611722</v>
       </c>
       <c r="C30">
-        <v>186.5711900299029</v>
+        <v>184.9649641801228</v>
       </c>
       <c r="D30">
-        <v>238.4551900299029</v>
+        <v>239.2519641801228</v>
       </c>
       <c r="E30">
-        <v>-57.916</v>
+        <v>-55.51299999999999</v>
       </c>
       <c r="F30">
-        <v>67.28400000000001</v>
+        <v>69.68700000000001</v>
       </c>
       <c r="G30">
         <v>15.4</v>
@@ -3747,28 +3747,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M30">
-        <v>3.653521200000001</v>
+        <v>3.784004100000001</v>
       </c>
       <c r="N30">
-        <v>20.25981213333333</v>
+        <v>20.12932923333333</v>
       </c>
       <c r="O30">
-        <v>4.862354912</v>
+        <v>4.831039016</v>
       </c>
       <c r="P30">
-        <v>15.39745722133333</v>
+        <v>15.29829021733333</v>
       </c>
       <c r="Q30">
-        <v>16.81745722133333</v>
+        <v>16.71829021733333</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.136658577370697</v>
+        <v>0.1377012131847496</v>
       </c>
       <c r="T30">
-        <v>1.250702517128897</v>
+        <v>1.265054791562648</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.545283857483386</v>
+        <v>6.31958441412189</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1097355813611722</v>
+        <v>0.1097499470154427</v>
       </c>
       <c r="C31">
-        <v>184.9649641801228</v>
+        <v>182.5082188501994</v>
       </c>
       <c r="D31">
-        <v>239.2519641801228</v>
+        <v>239.1982188501994</v>
       </c>
       <c r="E31">
-        <v>-55.51300000000001</v>
+        <v>-53.11</v>
       </c>
       <c r="F31">
-        <v>69.687</v>
+        <v>72.09</v>
       </c>
       <c r="G31">
         <v>15.4</v>
@@ -3829,45 +3829,45 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M31">
-        <v>3.7840041</v>
+        <v>3.986577</v>
       </c>
       <c r="N31">
-        <v>20.12932923333333</v>
+        <v>19.92675633333333</v>
       </c>
       <c r="O31">
-        <v>4.831039016</v>
+        <v>4.78242152</v>
       </c>
       <c r="P31">
-        <v>15.29829021733333</v>
+        <v>15.14433481333333</v>
       </c>
       <c r="Q31">
-        <v>16.71829021733333</v>
+        <v>16.56433481333333</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1377012131847496</v>
+        <v>0.1387736385934895</v>
       </c>
       <c r="T31">
-        <v>1.265054791562648</v>
+        <v>1.279817130980219</v>
       </c>
       <c r="U31">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V31">
         <v>0.24</v>
       </c>
       <c r="W31">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y31">
-        <v>6.319584414121891</v>
+        <v>5.998462674453129</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1097499470154427</v>
+        <v>0.1095439126697131</v>
       </c>
       <c r="C32">
-        <v>182.5082188501994</v>
+        <v>180.8783601033233</v>
       </c>
       <c r="D32">
-        <v>239.1982188501994</v>
+        <v>239.9713601033233</v>
       </c>
       <c r="E32">
-        <v>-53.11</v>
+        <v>-50.70699999999999</v>
       </c>
       <c r="F32">
-        <v>72.09</v>
+        <v>74.49300000000001</v>
       </c>
       <c r="G32">
         <v>15.4</v>
@@ -3911,28 +3911,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M32">
-        <v>3.986577</v>
+        <v>4.1194629</v>
       </c>
       <c r="N32">
-        <v>19.92675633333333</v>
+        <v>19.79387043333333</v>
       </c>
       <c r="O32">
-        <v>4.78242152</v>
+        <v>4.750528903999999</v>
       </c>
       <c r="P32">
-        <v>15.14433481333333</v>
+        <v>15.04334152933333</v>
       </c>
       <c r="Q32">
-        <v>16.56433481333333</v>
+        <v>16.46334152933333</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1387736385934895</v>
+        <v>0.1398771487966856</v>
       </c>
       <c r="T32">
-        <v>1.279817130980219</v>
+        <v>1.295007364293953</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.998462674453129</v>
+        <v>5.804963878503028</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1095439126697131</v>
+        <v>0.1093378783239835</v>
       </c>
       <c r="C33">
-        <v>180.8783601033233</v>
+        <v>179.2535154883776</v>
       </c>
       <c r="D33">
-        <v>239.9713601033233</v>
+        <v>240.7495154883776</v>
       </c>
       <c r="E33">
-        <v>-50.70699999999999</v>
+        <v>-48.304</v>
       </c>
       <c r="F33">
-        <v>74.49300000000001</v>
+        <v>76.896</v>
       </c>
       <c r="G33">
         <v>15.4</v>
@@ -3993,28 +3993,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M33">
-        <v>4.1194629</v>
+        <v>4.2523488</v>
       </c>
       <c r="N33">
-        <v>19.79387043333333</v>
+        <v>19.66098453333333</v>
       </c>
       <c r="O33">
-        <v>4.750528903999999</v>
+        <v>4.718636288</v>
       </c>
       <c r="P33">
-        <v>15.04334152933333</v>
+        <v>14.94234824533333</v>
       </c>
       <c r="Q33">
-        <v>16.46334152933333</v>
+        <v>16.36234824533334</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1398771487966856</v>
+        <v>0.1410131151823286</v>
       </c>
       <c r="T33">
-        <v>1.295007364293953</v>
+        <v>1.310644369175737</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.804963878503028</v>
+        <v>5.623558757299809</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1093378783239835</v>
+        <v>0.1091318439782539</v>
       </c>
       <c r="C34">
-        <v>179.2535154883776</v>
+        <v>177.633733942042</v>
       </c>
       <c r="D34">
-        <v>240.7495154883776</v>
+        <v>241.532733942042</v>
       </c>
       <c r="E34">
-        <v>-48.304</v>
+        <v>-45.901</v>
       </c>
       <c r="F34">
-        <v>76.896</v>
+        <v>79.29900000000001</v>
       </c>
       <c r="G34">
         <v>15.4</v>
@@ -4075,28 +4075,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M34">
-        <v>4.2523488</v>
+        <v>4.385234700000001</v>
       </c>
       <c r="N34">
-        <v>19.66098453333333</v>
+        <v>19.52809863333333</v>
       </c>
       <c r="O34">
-        <v>4.718636288</v>
+        <v>4.686743672</v>
       </c>
       <c r="P34">
-        <v>14.94234824533333</v>
+        <v>14.84135496133333</v>
       </c>
       <c r="Q34">
-        <v>16.36234824533334</v>
+        <v>16.26135496133333</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1410131151823286</v>
+        <v>0.1421829910123192</v>
       </c>
       <c r="T34">
-        <v>1.310644369175737</v>
+        <v>1.326748150322649</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.623558757299809</v>
+        <v>5.45314788586648</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1091318439782539</v>
+        <v>0.1089258096325243</v>
       </c>
       <c r="C35">
-        <v>177.633733942042</v>
+        <v>176.0190650398881</v>
       </c>
       <c r="D35">
-        <v>241.532733942042</v>
+        <v>242.3210650398881</v>
       </c>
       <c r="E35">
-        <v>-45.901</v>
+        <v>-43.49799999999999</v>
       </c>
       <c r="F35">
-        <v>79.29900000000001</v>
+        <v>81.70200000000001</v>
       </c>
       <c r="G35">
         <v>15.4</v>
@@ -4157,28 +4157,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M35">
-        <v>4.385234700000001</v>
+        <v>4.5181206</v>
       </c>
       <c r="N35">
-        <v>19.52809863333333</v>
+        <v>19.39521273333333</v>
       </c>
       <c r="O35">
-        <v>4.686743672</v>
+        <v>4.654851056</v>
       </c>
       <c r="P35">
-        <v>14.84135496133333</v>
+        <v>14.74036167733333</v>
       </c>
       <c r="Q35">
-        <v>16.26135496133333</v>
+        <v>16.16036167733333</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1421829910123192</v>
+        <v>0.1433883176250368</v>
       </c>
       <c r="T35">
-        <v>1.326748150322649</v>
+        <v>1.343339924837649</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.45314788586648</v>
+        <v>5.292761183340996</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1089258096325243</v>
+        <v>0.1087197752867947</v>
       </c>
       <c r="C36">
-        <v>176.0190650398881</v>
+        <v>174.4095590068392</v>
       </c>
       <c r="D36">
-        <v>242.3210650398881</v>
+        <v>243.1145590068392</v>
       </c>
       <c r="E36">
-        <v>-43.49799999999999</v>
+        <v>-41.09499999999998</v>
       </c>
       <c r="F36">
-        <v>81.70200000000001</v>
+        <v>84.10500000000002</v>
       </c>
       <c r="G36">
         <v>15.4</v>
@@ -4239,28 +4239,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M36">
-        <v>4.5181206</v>
+        <v>4.651006500000001</v>
       </c>
       <c r="N36">
-        <v>19.39521273333333</v>
+        <v>19.26232683333333</v>
       </c>
       <c r="O36">
-        <v>4.654851056</v>
+        <v>4.62295844</v>
       </c>
       <c r="P36">
-        <v>14.74036167733333</v>
+        <v>14.63936839333333</v>
       </c>
       <c r="Q36">
-        <v>16.16036167733333</v>
+        <v>16.05936839333333</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1433883176250368</v>
+        <v>0.1446307312104534</v>
       </c>
       <c r="T36">
-        <v>1.343339924837649</v>
+        <v>1.360442215491573</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.292761183340996</v>
+        <v>5.141539435245538</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1087197752867947</v>
+        <v>0.1085137409410651</v>
       </c>
       <c r="C37">
-        <v>174.4095590068392</v>
+        <v>172.8052667278374</v>
       </c>
       <c r="D37">
-        <v>243.1145590068392</v>
+        <v>243.9132667278374</v>
       </c>
       <c r="E37">
-        <v>-41.09499999999998</v>
+        <v>-38.69199999999999</v>
       </c>
       <c r="F37">
-        <v>84.10500000000002</v>
+        <v>86.50800000000001</v>
       </c>
       <c r="G37">
         <v>15.4</v>
@@ -4321,28 +4321,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M37">
-        <v>4.651006500000001</v>
+        <v>4.783892400000001</v>
       </c>
       <c r="N37">
-        <v>19.26232683333333</v>
+        <v>19.12944093333333</v>
       </c>
       <c r="O37">
-        <v>4.62295844</v>
+        <v>4.591065824</v>
       </c>
       <c r="P37">
-        <v>14.63936839333333</v>
+        <v>14.53837510933333</v>
       </c>
       <c r="Q37">
-        <v>16.05936839333333</v>
+        <v>15.95837510933333</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1446307312104534</v>
+        <v>0.1459119702204142</v>
       </c>
       <c r="T37">
-        <v>1.360442215491573</v>
+        <v>1.378078952728432</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.141539435245538</v>
+        <v>4.998718895377607</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1085137409410651</v>
+        <v>0.1083077065953355</v>
       </c>
       <c r="C38">
-        <v>172.8052667278375</v>
+        <v>171.2062397587211</v>
       </c>
       <c r="D38">
-        <v>243.9132667278375</v>
+        <v>244.7172397587211</v>
       </c>
       <c r="E38">
-        <v>-38.69200000000001</v>
+        <v>-36.289</v>
       </c>
       <c r="F38">
-        <v>86.508</v>
+        <v>88.911</v>
       </c>
       <c r="G38">
         <v>15.4</v>
@@ -4403,28 +4403,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M38">
-        <v>4.7838924</v>
+        <v>4.9167783</v>
       </c>
       <c r="N38">
-        <v>19.12944093333333</v>
+        <v>18.99655503333333</v>
       </c>
       <c r="O38">
-        <v>4.591065824</v>
+        <v>4.559173208</v>
       </c>
       <c r="P38">
-        <v>14.53837510933333</v>
+        <v>14.43738182533333</v>
       </c>
       <c r="Q38">
-        <v>15.95837510933333</v>
+        <v>15.85738182533333</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1459119702204142</v>
+        <v>0.1472338834846595</v>
       </c>
       <c r="T38">
-        <v>1.378078952728431</v>
+        <v>1.396275586385508</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.998718895377609</v>
+        <v>4.863618384691726</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1083077065953355</v>
+        <v>0.1081016722496059</v>
       </c>
       <c r="C39">
-        <v>171.2062397587211</v>
+        <v>169.6125303373179</v>
       </c>
       <c r="D39">
-        <v>244.7172397587211</v>
+        <v>245.526530337318</v>
       </c>
       <c r="E39">
-        <v>-36.289</v>
+        <v>-33.886</v>
       </c>
       <c r="F39">
-        <v>88.911</v>
+        <v>91.31400000000001</v>
       </c>
       <c r="G39">
         <v>15.4</v>
@@ -4485,28 +4485,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M39">
-        <v>4.9167783</v>
+        <v>5.0496642</v>
       </c>
       <c r="N39">
-        <v>18.99655503333333</v>
+        <v>18.86366913333333</v>
       </c>
       <c r="O39">
-        <v>4.559173208</v>
+        <v>4.527280591999999</v>
       </c>
       <c r="P39">
-        <v>14.43738182533333</v>
+        <v>14.33638854133333</v>
       </c>
       <c r="Q39">
-        <v>15.85738182533333</v>
+        <v>15.75638854133333</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1472338834846595</v>
+        <v>0.1485984391122676</v>
       </c>
       <c r="T39">
-        <v>1.396275586385508</v>
+        <v>1.41505920822507</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.863618384691726</v>
+        <v>4.735628427199838</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1081016722496059</v>
+        <v>0.1078956379038763</v>
       </c>
       <c r="C40">
-        <v>169.6125303373179</v>
+        <v>168.02419139476</v>
       </c>
       <c r="D40">
-        <v>245.526530337318</v>
+        <v>246.34119139476</v>
       </c>
       <c r="E40">
-        <v>-33.886</v>
+        <v>-31.48299999999999</v>
       </c>
       <c r="F40">
-        <v>91.31400000000001</v>
+        <v>93.71700000000001</v>
       </c>
       <c r="G40">
         <v>15.4</v>
@@ -4567,28 +4567,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M40">
-        <v>5.0496642</v>
+        <v>5.182550100000001</v>
       </c>
       <c r="N40">
-        <v>18.86366913333333</v>
+        <v>18.73078323333333</v>
       </c>
       <c r="O40">
-        <v>4.527280591999999</v>
+        <v>4.495387976</v>
       </c>
       <c r="P40">
-        <v>14.33638854133333</v>
+        <v>14.23539525733333</v>
       </c>
       <c r="Q40">
-        <v>15.75638854133333</v>
+        <v>15.65539525733333</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1485984391122676</v>
+        <v>0.1500077342686497</v>
       </c>
       <c r="T40">
-        <v>1.41505920822507</v>
+        <v>1.434458686518389</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.735628427199838</v>
+        <v>4.614202057271637</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1078956379038763</v>
+        <v>0.1084496035581467</v>
       </c>
       <c r="C41">
-        <v>168.02419139476</v>
+        <v>163.4429723556228</v>
       </c>
       <c r="D41">
-        <v>246.34119139476</v>
+        <v>244.1629723556229</v>
       </c>
       <c r="E41">
-        <v>-31.48299999999999</v>
+        <v>-29.08</v>
       </c>
       <c r="F41">
-        <v>93.71700000000001</v>
+        <v>96.12</v>
       </c>
       <c r="G41">
         <v>15.4</v>
@@ -4649,45 +4649,45 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M41">
-        <v>5.182550100000001</v>
+        <v>5.555736</v>
       </c>
       <c r="N41">
-        <v>18.73078323333333</v>
+        <v>18.35759733333333</v>
       </c>
       <c r="O41">
-        <v>4.495387976</v>
+        <v>4.40582336</v>
       </c>
       <c r="P41">
-        <v>14.23539525733333</v>
+        <v>13.95177397333334</v>
       </c>
       <c r="Q41">
-        <v>15.65539525733333</v>
+        <v>15.37177397333333</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1500077342686497</v>
+        <v>0.1514640059302446</v>
       </c>
       <c r="T41">
-        <v>1.434458686518389</v>
+        <v>1.454504814088152</v>
       </c>
       <c r="U41">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V41">
         <v>0.24</v>
       </c>
       <c r="W41">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>4.614202057271637</v>
+        <v>4.304260197628781</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1084496035581467</v>
+        <v>0.1082625692124171</v>
       </c>
       <c r="C42">
-        <v>163.4429723556228</v>
+        <v>161.7710799991562</v>
       </c>
       <c r="D42">
-        <v>244.1629723556229</v>
+        <v>244.8940799991562</v>
       </c>
       <c r="E42">
-        <v>-29.08</v>
+        <v>-26.67699999999999</v>
       </c>
       <c r="F42">
-        <v>96.12</v>
+        <v>98.52300000000001</v>
       </c>
       <c r="G42">
         <v>15.4</v>
@@ -4731,28 +4731,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M42">
-        <v>5.555736</v>
+        <v>5.694629400000001</v>
       </c>
       <c r="N42">
-        <v>18.35759733333333</v>
+        <v>18.21870393333333</v>
       </c>
       <c r="O42">
-        <v>4.40582336</v>
+        <v>4.372488944</v>
       </c>
       <c r="P42">
-        <v>13.95177397333334</v>
+        <v>13.84621498933333</v>
       </c>
       <c r="Q42">
-        <v>15.37177397333333</v>
+        <v>15.26621498933333</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1514640059302446</v>
+        <v>0.1529696427329104</v>
       </c>
       <c r="T42">
-        <v>1.454504814088152</v>
+        <v>1.475230471406042</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.304260197628781</v>
+        <v>4.199278241589054</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1082625692124171</v>
+        <v>0.1080755348666876</v>
       </c>
       <c r="C43">
-        <v>161.7710799991562</v>
+        <v>160.1035791662647</v>
       </c>
       <c r="D43">
-        <v>244.8940799991562</v>
+        <v>245.6295791662647</v>
       </c>
       <c r="E43">
-        <v>-26.67699999999999</v>
+        <v>-24.27399999999999</v>
       </c>
       <c r="F43">
-        <v>98.52300000000001</v>
+        <v>100.926</v>
       </c>
       <c r="G43">
         <v>15.4</v>
@@ -4813,28 +4813,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M43">
-        <v>5.694629400000001</v>
+        <v>5.833522800000002</v>
       </c>
       <c r="N43">
-        <v>18.21870393333333</v>
+        <v>18.07981053333333</v>
       </c>
       <c r="O43">
-        <v>4.372488944</v>
+        <v>4.339154528</v>
       </c>
       <c r="P43">
-        <v>13.84621498933333</v>
+        <v>13.74065600533333</v>
       </c>
       <c r="Q43">
-        <v>15.26621498933333</v>
+        <v>15.16065600533333</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1529696427329104</v>
+        <v>0.154527198046013</v>
       </c>
       <c r="T43">
-        <v>1.475230471406042</v>
+        <v>1.49667080656248</v>
       </c>
       <c r="U43">
         <v>0.0578</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.199278241589054</v>
+        <v>4.099295426313124</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1080755348666875</v>
+        <v>0.107888500520958</v>
       </c>
       <c r="C44">
-        <v>160.1035791662648</v>
+        <v>158.440509543802</v>
       </c>
       <c r="D44">
-        <v>245.6295791662648</v>
+        <v>246.3695095438021</v>
       </c>
       <c r="E44">
-        <v>-24.274</v>
+        <v>-21.871</v>
       </c>
       <c r="F44">
-        <v>100.926</v>
+        <v>103.329</v>
       </c>
       <c r="G44">
         <v>15.4</v>
@@ -4895,28 +4895,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M44">
-        <v>5.833522800000001</v>
+        <v>5.972416200000001</v>
       </c>
       <c r="N44">
-        <v>18.07981053333333</v>
+        <v>17.94091713333333</v>
       </c>
       <c r="O44">
-        <v>4.339154528</v>
+        <v>4.305820111999999</v>
       </c>
       <c r="P44">
-        <v>13.74065600533333</v>
+        <v>13.63509702133333</v>
       </c>
       <c r="Q44">
-        <v>15.16065600533333</v>
+        <v>15.05509702133333</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.154527198046013</v>
+        <v>0.1561394044227332</v>
       </c>
       <c r="T44">
-        <v>1.49667080656248</v>
+        <v>1.518863434180548</v>
       </c>
       <c r="U44">
         <v>0.0578</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.099295426313125</v>
+        <v>4.003962974538401</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.107888500520958</v>
+        <v>0.1088718661752284</v>
       </c>
       <c r="C45">
-        <v>158.440509543802</v>
+        <v>152.1963149092286</v>
       </c>
       <c r="D45">
-        <v>246.3695095438021</v>
+        <v>242.5283149092286</v>
       </c>
       <c r="E45">
-        <v>-21.871</v>
+        <v>-19.468</v>
       </c>
       <c r="F45">
-        <v>103.329</v>
+        <v>105.732</v>
       </c>
       <c r="G45">
         <v>15.4</v>
@@ -4977,45 +4977,45 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M45">
-        <v>5.972416200000001</v>
+        <v>6.4813716</v>
       </c>
       <c r="N45">
-        <v>17.94091713333333</v>
+        <v>17.43196173333333</v>
       </c>
       <c r="O45">
-        <v>4.305820111999999</v>
+        <v>4.183670816</v>
       </c>
       <c r="P45">
-        <v>13.63509702133333</v>
+        <v>13.24829091733334</v>
       </c>
       <c r="Q45">
-        <v>15.05509702133333</v>
+        <v>14.66829091733334</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1561394044227332</v>
+        <v>0.1578091895986221</v>
       </c>
       <c r="T45">
-        <v>1.518863434180548</v>
+        <v>1.541848655642118</v>
       </c>
       <c r="U45">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V45">
         <v>0.24</v>
       </c>
       <c r="W45">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>4.003962974538401</v>
+        <v>3.689548263724508</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1088718661752284</v>
+        <v>0.1087114318294988</v>
       </c>
       <c r="C46">
-        <v>152.1963149092286</v>
+        <v>150.4118014130618</v>
       </c>
       <c r="D46">
-        <v>242.5283149092286</v>
+        <v>243.1468014130618</v>
       </c>
       <c r="E46">
-        <v>-19.468</v>
+        <v>-17.065</v>
       </c>
       <c r="F46">
-        <v>105.732</v>
+        <v>108.135</v>
       </c>
       <c r="G46">
         <v>15.4</v>
@@ -5059,28 +5059,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M46">
-        <v>6.4813716</v>
+        <v>6.6286755</v>
       </c>
       <c r="N46">
-        <v>17.43196173333333</v>
+        <v>17.28465783333333</v>
       </c>
       <c r="O46">
-        <v>4.183670816</v>
+        <v>4.14831788</v>
       </c>
       <c r="P46">
-        <v>13.24829091733334</v>
+        <v>13.13633995333333</v>
       </c>
       <c r="Q46">
-        <v>14.66829091733334</v>
+        <v>14.55633995333333</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1578091895986221</v>
+        <v>0.1595396942354523</v>
       </c>
       <c r="T46">
-        <v>1.541848655642118</v>
+        <v>1.565669703338654</v>
       </c>
       <c r="U46">
         <v>0.0613</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.689548263724508</v>
+        <v>3.607558302308408</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1087114318294988</v>
+        <v>0.1085509974837692</v>
       </c>
       <c r="C47">
-        <v>150.4118014130618</v>
+        <v>148.6304504635176</v>
       </c>
       <c r="D47">
-        <v>243.1468014130618</v>
+        <v>243.7684504635176</v>
       </c>
       <c r="E47">
-        <v>-17.065</v>
+        <v>-14.66199999999999</v>
       </c>
       <c r="F47">
-        <v>108.135</v>
+        <v>110.538</v>
       </c>
       <c r="G47">
         <v>15.4</v>
@@ -5141,28 +5141,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M47">
-        <v>6.6286755</v>
+        <v>6.775979400000001</v>
       </c>
       <c r="N47">
-        <v>17.28465783333333</v>
+        <v>17.13735393333333</v>
       </c>
       <c r="O47">
-        <v>4.14831788</v>
+        <v>4.112964944</v>
       </c>
       <c r="P47">
-        <v>13.13633995333333</v>
+        <v>13.02438898933333</v>
       </c>
       <c r="Q47">
-        <v>14.55633995333333</v>
+        <v>14.44438898933333</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1595396942354523</v>
+        <v>0.1613342916366096</v>
       </c>
       <c r="T47">
-        <v>1.565669703338654</v>
+        <v>1.590373012060988</v>
       </c>
       <c r="U47">
         <v>0.0613</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.607558302308408</v>
+        <v>3.529133121823442</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1085509974837692</v>
+        <v>0.1093907231380396</v>
       </c>
       <c r="C48">
-        <v>148.6304504635176</v>
+        <v>143.0084491461146</v>
       </c>
       <c r="D48">
-        <v>243.7684504635176</v>
+        <v>240.5494491461147</v>
       </c>
       <c r="E48">
-        <v>-14.66199999999999</v>
+        <v>-12.25899999999999</v>
       </c>
       <c r="F48">
-        <v>110.538</v>
+        <v>112.941</v>
       </c>
       <c r="G48">
         <v>15.4</v>
@@ -5223,45 +5223,45 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M48">
-        <v>6.775979400000001</v>
+        <v>7.239518100000002</v>
       </c>
       <c r="N48">
-        <v>17.13735393333333</v>
+        <v>16.67381523333333</v>
       </c>
       <c r="O48">
-        <v>4.112964944</v>
+        <v>4.001715656</v>
       </c>
       <c r="P48">
-        <v>13.02438898933333</v>
+        <v>12.67209957733333</v>
       </c>
       <c r="Q48">
-        <v>14.44438898933333</v>
+        <v>14.09209957733333</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1613342916366096</v>
+        <v>0.1631966096944143</v>
       </c>
       <c r="T48">
-        <v>1.590373012060988</v>
+        <v>1.616008521112466</v>
       </c>
       <c r="U48">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V48">
         <v>0.24</v>
       </c>
       <c r="W48">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>3.529133121823442</v>
+        <v>3.303166454315976</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1093907231380396</v>
+        <v>0.10925156879231</v>
       </c>
       <c r="C49">
-        <v>143.0084491461146</v>
+        <v>141.132993253355</v>
       </c>
       <c r="D49">
-        <v>240.5494491461147</v>
+        <v>241.076993253355</v>
       </c>
       <c r="E49">
-        <v>-12.25899999999999</v>
+        <v>-9.855999999999995</v>
       </c>
       <c r="F49">
-        <v>112.941</v>
+        <v>115.344</v>
       </c>
       <c r="G49">
         <v>15.4</v>
@@ -5305,28 +5305,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M49">
-        <v>7.239518100000002</v>
+        <v>7.393550400000001</v>
       </c>
       <c r="N49">
-        <v>16.67381523333333</v>
+        <v>16.51978293333333</v>
       </c>
       <c r="O49">
-        <v>4.001715656</v>
+        <v>3.964747903999999</v>
       </c>
       <c r="P49">
-        <v>12.67209957733333</v>
+        <v>12.55503502933333</v>
       </c>
       <c r="Q49">
-        <v>14.09209957733333</v>
+        <v>13.97503502933333</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1631966096944143</v>
+        <v>0.1651305553698269</v>
       </c>
       <c r="T49">
-        <v>1.616008521112466</v>
+        <v>1.642630011281309</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.303166454315976</v>
+        <v>3.234350486517726</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.10925156879231</v>
+        <v>0.1091124144465804</v>
       </c>
       <c r="C50">
-        <v>141.132993253355</v>
+        <v>139.2598563388157</v>
       </c>
       <c r="D50">
-        <v>241.076993253355</v>
+        <v>241.6068563388157</v>
       </c>
       <c r="E50">
-        <v>-9.856000000000009</v>
+        <v>-7.453000000000003</v>
       </c>
       <c r="F50">
-        <v>115.344</v>
+        <v>117.747</v>
       </c>
       <c r="G50">
         <v>15.4</v>
@@ -5387,28 +5387,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M50">
-        <v>7.393550400000001</v>
+        <v>7.5475827</v>
       </c>
       <c r="N50">
-        <v>16.51978293333333</v>
+        <v>16.36575063333333</v>
       </c>
       <c r="O50">
-        <v>3.964747903999999</v>
+        <v>3.927780152</v>
       </c>
       <c r="P50">
-        <v>12.55503502933333</v>
+        <v>12.43797048133333</v>
       </c>
       <c r="Q50">
-        <v>13.97503502933333</v>
+        <v>13.85797048133333</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1651305553698269</v>
+        <v>0.1671403420521184</v>
       </c>
       <c r="T50">
-        <v>1.642630011281309</v>
+        <v>1.670295481456774</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.234350486517727</v>
+        <v>3.168343333731651</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1091124144465804</v>
+        <v>0.1089732601008508</v>
       </c>
       <c r="C51">
-        <v>139.2598563388157</v>
+        <v>137.3890537268236</v>
       </c>
       <c r="D51">
-        <v>241.6068563388157</v>
+        <v>242.1390537268236</v>
       </c>
       <c r="E51">
-        <v>-7.453000000000003</v>
+        <v>-5.049999999999997</v>
       </c>
       <c r="F51">
-        <v>117.747</v>
+        <v>120.15</v>
       </c>
       <c r="G51">
         <v>15.4</v>
@@ -5469,28 +5469,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M51">
-        <v>7.5475827</v>
+        <v>7.701615000000001</v>
       </c>
       <c r="N51">
-        <v>16.36575063333333</v>
+        <v>16.21171833333333</v>
       </c>
       <c r="O51">
-        <v>3.927780152</v>
+        <v>3.8908124</v>
       </c>
       <c r="P51">
-        <v>12.43797048133333</v>
+        <v>12.32090593333333</v>
       </c>
       <c r="Q51">
-        <v>13.85797048133333</v>
+        <v>13.74090593333333</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1671403420521184</v>
+        <v>0.1692305202017016</v>
       </c>
       <c r="T51">
-        <v>1.670295481456774</v>
+        <v>1.699067570439257</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.168343333731651</v>
+        <v>3.104976467057017</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1089732601008508</v>
+        <v>0.1088341057551212</v>
       </c>
       <c r="C52">
-        <v>137.3890537268236</v>
+        <v>135.5206008770256</v>
       </c>
       <c r="D52">
-        <v>242.1390537268236</v>
+        <v>242.6736008770256</v>
       </c>
       <c r="E52">
-        <v>-5.049999999999997</v>
+        <v>-2.646999999999991</v>
       </c>
       <c r="F52">
-        <v>120.15</v>
+        <v>122.553</v>
       </c>
       <c r="G52">
         <v>15.4</v>
@@ -5551,28 +5551,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M52">
-        <v>7.701615000000001</v>
+        <v>7.855647300000001</v>
       </c>
       <c r="N52">
-        <v>16.21171833333333</v>
+        <v>16.05768603333333</v>
       </c>
       <c r="O52">
-        <v>3.8908124</v>
+        <v>3.853844648</v>
       </c>
       <c r="P52">
-        <v>12.32090593333333</v>
+        <v>12.20384138533333</v>
       </c>
       <c r="Q52">
-        <v>13.74090593333333</v>
+        <v>13.62384138533333</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1692305202017016</v>
+        <v>0.1714060117451454</v>
       </c>
       <c r="T52">
-        <v>1.699067570439257</v>
+        <v>1.729014030400617</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.104976467057017</v>
+        <v>3.044094575546096</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1088341057551212</v>
+        <v>0.1117775114093916</v>
       </c>
       <c r="C53">
-        <v>135.5206008770256</v>
+        <v>122.2913839781882</v>
       </c>
       <c r="D53">
-        <v>242.6736008770256</v>
+        <v>231.8473839781882</v>
       </c>
       <c r="E53">
-        <v>-2.646999999999991</v>
+        <v>-0.2439999999999856</v>
       </c>
       <c r="F53">
-        <v>122.553</v>
+        <v>124.956</v>
       </c>
       <c r="G53">
         <v>15.4</v>
@@ -5633,45 +5633,45 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M53">
-        <v>7.855647300000001</v>
+        <v>8.984336400000002</v>
       </c>
       <c r="N53">
-        <v>16.05768603333333</v>
+        <v>14.92899693333333</v>
       </c>
       <c r="O53">
-        <v>3.853844648</v>
+        <v>3.582959263999999</v>
       </c>
       <c r="P53">
-        <v>12.20384138533333</v>
+        <v>11.34603766933333</v>
       </c>
       <c r="Q53">
-        <v>13.62384138533333</v>
+        <v>12.76603766933333</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1714060117451454</v>
+        <v>0.1736721487695659</v>
       </c>
       <c r="T53">
-        <v>1.729014030400617</v>
+        <v>1.760208259527033</v>
       </c>
       <c r="U53">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V53">
         <v>0.24</v>
       </c>
       <c r="W53">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>3.044094575546096</v>
+        <v>2.66166940647206</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1117775114093916</v>
+        <v>0.111697637063662</v>
       </c>
       <c r="C54">
-        <v>122.2913839781882</v>
+        <v>120.1694055584686</v>
       </c>
       <c r="D54">
-        <v>231.8473839781882</v>
+        <v>232.1284055584686</v>
       </c>
       <c r="E54">
-        <v>-0.2439999999999856</v>
+        <v>2.159000000000006</v>
       </c>
       <c r="F54">
-        <v>124.956</v>
+        <v>127.359</v>
       </c>
       <c r="G54">
         <v>15.4</v>
@@ -5715,28 +5715,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M54">
-        <v>8.984336400000002</v>
+        <v>9.157112100000001</v>
       </c>
       <c r="N54">
-        <v>14.92899693333333</v>
+        <v>14.75622123333333</v>
       </c>
       <c r="O54">
-        <v>3.582959263999999</v>
+        <v>3.541493096</v>
       </c>
       <c r="P54">
-        <v>11.34603766933333</v>
+        <v>11.21472813733333</v>
       </c>
       <c r="Q54">
-        <v>12.76603766933333</v>
+        <v>12.63472813733333</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1736721487695659</v>
+        <v>0.1760347171567277</v>
       </c>
       <c r="T54">
-        <v>1.760208259527033</v>
+        <v>1.792729902658829</v>
       </c>
       <c r="U54">
         <v>0.07190000000000001</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.66166940647206</v>
+        <v>2.611449228991456</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.111697637063662</v>
+        <v>0.1116177627179324</v>
       </c>
       <c r="C55">
-        <v>120.1694055584686</v>
+        <v>118.0481092164718</v>
       </c>
       <c r="D55">
-        <v>232.1284055584686</v>
+        <v>232.4101092164719</v>
       </c>
       <c r="E55">
-        <v>2.159000000000006</v>
+        <v>4.562000000000026</v>
       </c>
       <c r="F55">
-        <v>127.359</v>
+        <v>129.762</v>
       </c>
       <c r="G55">
         <v>15.4</v>
@@ -5797,28 +5797,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M55">
-        <v>9.157112100000001</v>
+        <v>9.329887800000003</v>
       </c>
       <c r="N55">
-        <v>14.75622123333333</v>
+        <v>14.58344553333333</v>
       </c>
       <c r="O55">
-        <v>3.541493096</v>
+        <v>3.500026927999999</v>
       </c>
       <c r="P55">
-        <v>11.21472813733333</v>
+        <v>11.08341860533333</v>
       </c>
       <c r="Q55">
-        <v>12.63472813733333</v>
+        <v>12.50341860533333</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1760347171567277</v>
+        <v>0.1785000059085488</v>
       </c>
       <c r="T55">
-        <v>1.792729902658829</v>
+        <v>1.826665530274616</v>
       </c>
       <c r="U55">
         <v>0.07190000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.611449228991456</v>
+        <v>2.563089058084206</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1116177627179324</v>
+        <v>0.1115378883722028</v>
       </c>
       <c r="C56">
-        <v>118.0481092164718</v>
+        <v>115.927497438459</v>
       </c>
       <c r="D56">
-        <v>232.4101092164719</v>
+        <v>232.692497438459</v>
       </c>
       <c r="E56">
-        <v>4.562000000000026</v>
+        <v>6.965000000000018</v>
       </c>
       <c r="F56">
-        <v>129.762</v>
+        <v>132.165</v>
       </c>
       <c r="G56">
         <v>15.4</v>
@@ -5879,28 +5879,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M56">
-        <v>9.329887800000003</v>
+        <v>9.502663500000002</v>
       </c>
       <c r="N56">
-        <v>14.58344553333333</v>
+        <v>14.41066983333333</v>
       </c>
       <c r="O56">
-        <v>3.500026927999999</v>
+        <v>3.45856076</v>
       </c>
       <c r="P56">
-        <v>11.08341860533333</v>
+        <v>10.95210907333333</v>
       </c>
       <c r="Q56">
-        <v>12.50341860533333</v>
+        <v>12.37210907333333</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1785000059085488</v>
+        <v>0.1810748630493396</v>
       </c>
       <c r="T56">
-        <v>1.826665530274616</v>
+        <v>1.86210940800666</v>
       </c>
       <c r="U56">
         <v>0.07190000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.563089058084206</v>
+        <v>2.516487438846312</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1115378883722028</v>
+        <v>0.1131178540264732</v>
       </c>
       <c r="C57">
-        <v>115.927497438459</v>
+        <v>108.0631505301842</v>
       </c>
       <c r="D57">
-        <v>232.692497438459</v>
+        <v>227.2311505301842</v>
       </c>
       <c r="E57">
-        <v>6.965000000000018</v>
+        <v>9.368000000000009</v>
       </c>
       <c r="F57">
-        <v>132.165</v>
+        <v>134.568</v>
       </c>
       <c r="G57">
         <v>15.4</v>
@@ -5961,45 +5961,45 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M57">
-        <v>9.502663500000002</v>
+        <v>10.2002544</v>
       </c>
       <c r="N57">
-        <v>14.41066983333333</v>
+        <v>13.71307893333333</v>
       </c>
       <c r="O57">
-        <v>3.45856076</v>
+        <v>3.291138944</v>
       </c>
       <c r="P57">
-        <v>10.95210907333333</v>
+        <v>10.42193998933333</v>
       </c>
       <c r="Q57">
-        <v>12.37210907333333</v>
+        <v>11.84193998933333</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1810748630493396</v>
+        <v>0.1837667591510756</v>
       </c>
       <c r="T57">
-        <v>1.86210940800666</v>
+        <v>1.899164371090161</v>
       </c>
       <c r="U57">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V57">
         <v>0.24</v>
       </c>
       <c r="W57">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y57">
-        <v>2.516487438846312</v>
+        <v>2.344385972700183</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1131178540264732</v>
+        <v>0.1130676196807437</v>
       </c>
       <c r="C58">
-        <v>108.0631505301842</v>
+        <v>105.8298429948565</v>
       </c>
       <c r="D58">
-        <v>227.2311505301842</v>
+        <v>227.4008429948565</v>
       </c>
       <c r="E58">
-        <v>9.368000000000009</v>
+        <v>11.77100000000003</v>
       </c>
       <c r="F58">
-        <v>134.568</v>
+        <v>136.971</v>
       </c>
       <c r="G58">
         <v>15.4</v>
@@ -6043,28 +6043,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M58">
-        <v>10.2002544</v>
+        <v>10.3824018</v>
       </c>
       <c r="N58">
-        <v>13.71307893333333</v>
+        <v>13.53093153333333</v>
       </c>
       <c r="O58">
-        <v>3.291138944</v>
+        <v>3.247423567999999</v>
       </c>
       <c r="P58">
-        <v>10.42193998933333</v>
+        <v>10.28350796533333</v>
       </c>
       <c r="Q58">
-        <v>11.84193998933333</v>
+        <v>11.70350796533333</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1837667591510756</v>
+        <v>0.1865838597226597</v>
       </c>
       <c r="T58">
-        <v>1.899164371090161</v>
+        <v>1.937942820828709</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.344385972700183</v>
+        <v>2.303256394231759</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1130676196807437</v>
+        <v>0.1130173853350141</v>
       </c>
       <c r="C59">
-        <v>105.8298429948565</v>
+        <v>103.596789095992</v>
       </c>
       <c r="D59">
-        <v>227.4008429948565</v>
+        <v>227.570789095992</v>
       </c>
       <c r="E59">
-        <v>11.77100000000003</v>
+        <v>14.17400000000002</v>
       </c>
       <c r="F59">
-        <v>136.971</v>
+        <v>139.374</v>
       </c>
       <c r="G59">
         <v>15.4</v>
@@ -6125,28 +6125,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M59">
-        <v>10.3824018</v>
+        <v>10.5645492</v>
       </c>
       <c r="N59">
-        <v>13.53093153333333</v>
+        <v>13.34878413333333</v>
       </c>
       <c r="O59">
-        <v>3.247423567999999</v>
+        <v>3.203708192</v>
       </c>
       <c r="P59">
-        <v>10.28350796533333</v>
+        <v>10.14507594133333</v>
       </c>
       <c r="Q59">
-        <v>11.70350796533333</v>
+        <v>11.56507594133333</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1865838597226597</v>
+        <v>0.1895351079405097</v>
       </c>
       <c r="T59">
-        <v>1.937942820828709</v>
+        <v>1.978567863411949</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.303256394231759</v>
+        <v>2.263545077089833</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1130173853350141</v>
+        <v>0.1129671509892845</v>
       </c>
       <c r="C60">
-        <v>103.596789095992</v>
+        <v>101.3639894026751</v>
       </c>
       <c r="D60">
-        <v>227.570789095992</v>
+        <v>227.740989402675</v>
       </c>
       <c r="E60">
-        <v>14.17399999999999</v>
+        <v>16.57699999999998</v>
       </c>
       <c r="F60">
-        <v>139.374</v>
+        <v>141.777</v>
       </c>
       <c r="G60">
         <v>15.4</v>
@@ -6207,28 +6207,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M60">
-        <v>10.5645492</v>
+        <v>10.7466966</v>
       </c>
       <c r="N60">
-        <v>13.34878413333333</v>
+        <v>13.16663673333333</v>
       </c>
       <c r="O60">
-        <v>3.203708192</v>
+        <v>3.159992816</v>
       </c>
       <c r="P60">
-        <v>10.14507594133333</v>
+        <v>10.00664391733334</v>
       </c>
       <c r="Q60">
-        <v>11.56507594133333</v>
+        <v>11.42664391733333</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1895351079405097</v>
+        <v>0.1926303194860597</v>
       </c>
       <c r="T60">
-        <v>1.978567863411949</v>
+        <v>2.021174615389493</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.263545077089833</v>
+        <v>2.2251799062917</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1129671509892845</v>
+        <v>0.1129169166435549</v>
       </c>
       <c r="C61">
-        <v>101.3639894026751</v>
+        <v>99.131444485694</v>
       </c>
       <c r="D61">
-        <v>227.740989402675</v>
+        <v>227.911444485694</v>
       </c>
       <c r="E61">
-        <v>16.57699999999998</v>
+        <v>18.98</v>
       </c>
       <c r="F61">
-        <v>141.777</v>
+        <v>144.18</v>
       </c>
       <c r="G61">
         <v>15.4</v>
@@ -6289,28 +6289,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M61">
-        <v>10.7466966</v>
+        <v>10.928844</v>
       </c>
       <c r="N61">
-        <v>13.16663673333333</v>
+        <v>12.98448933333333</v>
       </c>
       <c r="O61">
-        <v>3.159992816</v>
+        <v>3.11627744</v>
       </c>
       <c r="P61">
-        <v>10.00664391733334</v>
+        <v>9.868211893333333</v>
       </c>
       <c r="Q61">
-        <v>11.42664391733333</v>
+        <v>11.28821189333333</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1926303194860597</v>
+        <v>0.1958802916088872</v>
       </c>
       <c r="T61">
-        <v>2.021174615389493</v>
+        <v>2.065911704965914</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.2251799062917</v>
+        <v>2.188093574520172</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1129169166435549</v>
+        <v>0.1128666822978253</v>
       </c>
       <c r="C62">
-        <v>99.131444485694</v>
+        <v>96.89915491754724</v>
       </c>
       <c r="D62">
-        <v>227.911444485694</v>
+        <v>228.0821549175472</v>
       </c>
       <c r="E62">
-        <v>18.98</v>
+        <v>21.383</v>
       </c>
       <c r="F62">
-        <v>144.18</v>
+        <v>146.583</v>
       </c>
       <c r="G62">
         <v>15.4</v>
@@ -6371,28 +6371,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M62">
-        <v>10.928844</v>
+        <v>11.1109914</v>
       </c>
       <c r="N62">
-        <v>12.98448933333333</v>
+        <v>12.80234193333333</v>
       </c>
       <c r="O62">
-        <v>3.11627744</v>
+        <v>3.072562064</v>
       </c>
       <c r="P62">
-        <v>9.868211893333333</v>
+        <v>9.729779869333333</v>
       </c>
       <c r="Q62">
-        <v>11.28821189333333</v>
+        <v>11.14977986933333</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1958802916088872</v>
+        <v>0.1992969289687828</v>
       </c>
       <c r="T62">
-        <v>2.065911704965914</v>
+        <v>2.112943004264204</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.188093574520172</v>
+        <v>2.152223188052628</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1128666822978253</v>
+        <v>0.1128164479520957</v>
       </c>
       <c r="C63">
-        <v>96.89915491754724</v>
+        <v>94.66712127244966</v>
       </c>
       <c r="D63">
-        <v>228.0821549175472</v>
+        <v>228.2531212724497</v>
       </c>
       <c r="E63">
-        <v>21.383</v>
+        <v>23.78600000000002</v>
       </c>
       <c r="F63">
-        <v>146.583</v>
+        <v>148.986</v>
       </c>
       <c r="G63">
         <v>15.4</v>
@@ -6453,28 +6453,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M63">
-        <v>11.1109914</v>
+        <v>11.2931388</v>
       </c>
       <c r="N63">
-        <v>12.80234193333333</v>
+        <v>12.62019453333333</v>
       </c>
       <c r="O63">
-        <v>3.072562064</v>
+        <v>3.028846687999999</v>
       </c>
       <c r="P63">
-        <v>9.729779869333333</v>
+        <v>9.591347845333331</v>
       </c>
       <c r="Q63">
-        <v>11.14977986933333</v>
+        <v>11.01134784533333</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1992969289687828</v>
+        <v>0.2028933893476202</v>
       </c>
       <c r="T63">
-        <v>2.112943004264204</v>
+        <v>2.162449635104509</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.152223188052628</v>
+        <v>2.117509910825972</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1128164479520957</v>
+        <v>0.1127662136063661</v>
       </c>
       <c r="C64">
-        <v>94.66712127244966</v>
+        <v>92.43534412633934</v>
       </c>
       <c r="D64">
-        <v>228.2531212724497</v>
+        <v>228.4243441263393</v>
       </c>
       <c r="E64">
-        <v>23.78600000000002</v>
+        <v>26.18900000000001</v>
       </c>
       <c r="F64">
-        <v>148.986</v>
+        <v>151.389</v>
       </c>
       <c r="G64">
         <v>15.4</v>
@@ -6535,28 +6535,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M64">
-        <v>11.2931388</v>
+        <v>11.4752862</v>
       </c>
       <c r="N64">
-        <v>12.62019453333333</v>
+        <v>12.43804713333333</v>
       </c>
       <c r="O64">
-        <v>3.028846687999999</v>
+        <v>2.985131312</v>
       </c>
       <c r="P64">
-        <v>9.591347845333331</v>
+        <v>9.452915821333333</v>
       </c>
       <c r="Q64">
-        <v>11.01134784533333</v>
+        <v>10.87291582133333</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2028933893476202</v>
+        <v>0.2066842529901786</v>
       </c>
       <c r="T64">
-        <v>2.162449635104509</v>
+        <v>2.214632300044289</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.117509910825972</v>
+        <v>2.083898642400164</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1127662136063661</v>
+        <v>0.1127159792606365</v>
       </c>
       <c r="C65">
-        <v>92.43534412633934</v>
+        <v>90.20382405688324</v>
       </c>
       <c r="D65">
-        <v>228.4243441263393</v>
+        <v>228.5958240568832</v>
       </c>
       <c r="E65">
-        <v>26.18900000000001</v>
+        <v>28.592</v>
       </c>
       <c r="F65">
-        <v>151.389</v>
+        <v>153.792</v>
       </c>
       <c r="G65">
         <v>15.4</v>
@@ -6617,28 +6617,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M65">
-        <v>11.4752862</v>
+        <v>11.6574336</v>
       </c>
       <c r="N65">
-        <v>12.43804713333333</v>
+        <v>12.25589973333333</v>
       </c>
       <c r="O65">
-        <v>2.985131312</v>
+        <v>2.941415936</v>
       </c>
       <c r="P65">
-        <v>9.452915821333333</v>
+        <v>9.314483797333333</v>
       </c>
       <c r="Q65">
-        <v>10.87291582133333</v>
+        <v>10.73448379733333</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2066842529901786</v>
+        <v>0.2106857201684347</v>
       </c>
       <c r="T65">
-        <v>2.214632300044289</v>
+        <v>2.269714001925169</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.083898642400164</v>
+        <v>2.051337726112661</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1127159792606365</v>
+        <v>0.1126657449149069</v>
       </c>
       <c r="C66">
-        <v>90.20382405688324</v>
+        <v>87.97256164348497</v>
       </c>
       <c r="D66">
-        <v>228.5958240568832</v>
+        <v>228.767561643485</v>
       </c>
       <c r="E66">
-        <v>28.592</v>
+        <v>30.99500000000002</v>
       </c>
       <c r="F66">
-        <v>153.792</v>
+        <v>156.195</v>
       </c>
       <c r="G66">
         <v>15.4</v>
@@ -6699,28 +6699,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M66">
-        <v>11.6574336</v>
+        <v>11.839581</v>
       </c>
       <c r="N66">
-        <v>12.25589973333333</v>
+        <v>12.07375233333333</v>
       </c>
       <c r="O66">
-        <v>2.941415936</v>
+        <v>2.89770056</v>
       </c>
       <c r="P66">
-        <v>9.314483797333333</v>
+        <v>9.176051773333331</v>
       </c>
       <c r="Q66">
-        <v>10.73448379733333</v>
+        <v>10.59605177333333</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2106857201684347</v>
+        <v>0.2149158426140198</v>
       </c>
       <c r="T66">
-        <v>2.269714001925169</v>
+        <v>2.327943229627814</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.051337726112661</v>
+        <v>2.019778684172466</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1126657449149069</v>
+        <v>0.1197382305691773</v>
       </c>
       <c r="C67">
-        <v>87.97256164348497</v>
+        <v>63.68703503403097</v>
       </c>
       <c r="D67">
-        <v>228.767561643485</v>
+        <v>206.885035034031</v>
       </c>
       <c r="E67">
-        <v>30.99500000000002</v>
+        <v>33.39800000000001</v>
       </c>
       <c r="F67">
-        <v>156.195</v>
+        <v>158.598</v>
       </c>
       <c r="G67">
         <v>15.4</v>
@@ -6781,45 +6781,45 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M67">
-        <v>11.839581</v>
+        <v>14.27382</v>
       </c>
       <c r="N67">
-        <v>12.07375233333333</v>
+        <v>9.639513333333333</v>
       </c>
       <c r="O67">
-        <v>2.89770056</v>
+        <v>2.3134832</v>
       </c>
       <c r="P67">
-        <v>9.176051773333331</v>
+        <v>7.326030133333333</v>
       </c>
       <c r="Q67">
-        <v>10.59605177333333</v>
+        <v>8.746030133333333</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2149158426140198</v>
+        <v>0.219394795791698</v>
       </c>
       <c r="T67">
-        <v>2.327943229627814</v>
+        <v>2.389597706018848</v>
       </c>
       <c r="U67">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V67">
         <v>0.24</v>
       </c>
       <c r="W67">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.019778684172466</v>
+        <v>1.675328211602313</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1197382305691773</v>
+        <v>0.1197959162234477</v>
       </c>
       <c r="C68">
-        <v>63.68703503403097</v>
+        <v>61.12275182795975</v>
       </c>
       <c r="D68">
-        <v>206.885035034031</v>
+        <v>206.7237518279597</v>
       </c>
       <c r="E68">
-        <v>33.39800000000001</v>
+        <v>35.801</v>
       </c>
       <c r="F68">
-        <v>158.598</v>
+        <v>161.001</v>
       </c>
       <c r="G68">
         <v>15.4</v>
@@ -6863,28 +6863,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M68">
-        <v>14.27382</v>
+        <v>14.49009</v>
       </c>
       <c r="N68">
-        <v>9.639513333333333</v>
+        <v>9.423243333333334</v>
       </c>
       <c r="O68">
-        <v>2.3134832</v>
+        <v>2.2615784</v>
       </c>
       <c r="P68">
-        <v>7.326030133333333</v>
+        <v>7.161664933333334</v>
       </c>
       <c r="Q68">
-        <v>8.746030133333333</v>
+        <v>8.581664933333334</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.219394795791698</v>
+        <v>0.2241452006771144</v>
       </c>
       <c r="T68">
-        <v>2.389597706018848</v>
+        <v>2.454988817342673</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.675328211602313</v>
+        <v>1.650323312921682</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1197959162234477</v>
+        <v>0.1198536018777181</v>
       </c>
       <c r="C69">
-        <v>61.12275182795975</v>
+        <v>58.55871989196939</v>
       </c>
       <c r="D69">
-        <v>206.7237518279597</v>
+        <v>206.5627198919694</v>
       </c>
       <c r="E69">
-        <v>35.801</v>
+        <v>38.20400000000002</v>
       </c>
       <c r="F69">
-        <v>161.001</v>
+        <v>163.404</v>
       </c>
       <c r="G69">
         <v>15.4</v>
@@ -6945,28 +6945,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M69">
-        <v>14.49009</v>
+        <v>14.70636</v>
       </c>
       <c r="N69">
-        <v>9.423243333333334</v>
+        <v>9.206973333333332</v>
       </c>
       <c r="O69">
-        <v>2.2615784</v>
+        <v>2.209673599999999</v>
       </c>
       <c r="P69">
-        <v>7.161664933333334</v>
+        <v>6.997299733333333</v>
       </c>
       <c r="Q69">
-        <v>8.581664933333334</v>
+        <v>8.417299733333333</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2241452006771144</v>
+        <v>0.2291925058678692</v>
       </c>
       <c r="T69">
-        <v>2.454988817342673</v>
+        <v>2.524466873124237</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.650323312921682</v>
+        <v>1.626053852437539</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1198536018777181</v>
+        <v>0.1199112875319885</v>
       </c>
       <c r="C70">
-        <v>58.55871989196939</v>
+        <v>55.99493863932011</v>
       </c>
       <c r="D70">
-        <v>206.5627198919694</v>
+        <v>206.4019386393201</v>
       </c>
       <c r="E70">
-        <v>38.20400000000002</v>
+        <v>40.60700000000001</v>
       </c>
       <c r="F70">
-        <v>163.404</v>
+        <v>165.807</v>
       </c>
       <c r="G70">
         <v>15.4</v>
@@ -7027,28 +7027,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M70">
-        <v>14.70636</v>
+        <v>14.92263</v>
       </c>
       <c r="N70">
-        <v>9.206973333333332</v>
+        <v>8.990703333333332</v>
       </c>
       <c r="O70">
-        <v>2.209673599999999</v>
+        <v>2.157768799999999</v>
       </c>
       <c r="P70">
-        <v>6.997299733333333</v>
+        <v>6.832934533333333</v>
       </c>
       <c r="Q70">
-        <v>8.417299733333333</v>
+        <v>8.252934533333333</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2291925058678692</v>
+        <v>0.234565443651576</v>
       </c>
       <c r="T70">
-        <v>2.524466873124237</v>
+        <v>2.598427384117515</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.626053852437539</v>
+        <v>1.602487854576126</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1199112875319885</v>
+        <v>0.1199689731862589</v>
       </c>
       <c r="C71">
-        <v>55.99493863932011</v>
+        <v>53.43140748509759</v>
       </c>
       <c r="D71">
-        <v>206.4019386393201</v>
+        <v>206.2414074850976</v>
       </c>
       <c r="E71">
-        <v>40.60700000000001</v>
+        <v>43.01000000000003</v>
       </c>
       <c r="F71">
-        <v>165.807</v>
+        <v>168.21</v>
       </c>
       <c r="G71">
         <v>15.4</v>
@@ -7109,28 +7109,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M71">
-        <v>14.92263</v>
+        <v>15.1389</v>
       </c>
       <c r="N71">
-        <v>8.990703333333332</v>
+        <v>8.774433333333331</v>
       </c>
       <c r="O71">
-        <v>2.157768799999999</v>
+        <v>2.105864</v>
       </c>
       <c r="P71">
-        <v>6.832934533333333</v>
+        <v>6.668569333333331</v>
       </c>
       <c r="Q71">
-        <v>8.252934533333333</v>
+        <v>8.088569333333332</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.234565443651576</v>
+        <v>0.2402965772875298</v>
       </c>
       <c r="T71">
-        <v>2.598427384117515</v>
+        <v>2.677318595843678</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.602487854576126</v>
+        <v>1.579595170939324</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1199689731862589</v>
+        <v>0.1200266588405294</v>
       </c>
       <c r="C72">
-        <v>53.43140748509759</v>
+        <v>50.86812584620571</v>
       </c>
       <c r="D72">
-        <v>206.2414074850976</v>
+        <v>206.0811258462057</v>
       </c>
       <c r="E72">
-        <v>43.01000000000003</v>
+        <v>45.41300000000003</v>
       </c>
       <c r="F72">
-        <v>168.21</v>
+        <v>170.613</v>
       </c>
       <c r="G72">
         <v>15.4</v>
@@ -7191,28 +7191,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M72">
-        <v>15.1389</v>
+        <v>15.35517</v>
       </c>
       <c r="N72">
-        <v>8.774433333333331</v>
+        <v>8.558163333333333</v>
       </c>
       <c r="O72">
-        <v>2.105864</v>
+        <v>2.0539592</v>
       </c>
       <c r="P72">
-        <v>6.668569333333331</v>
+        <v>6.504204133333333</v>
       </c>
       <c r="Q72">
-        <v>8.088569333333332</v>
+        <v>7.924204133333333</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2402965772875298</v>
+        <v>0.2464229615190668</v>
       </c>
       <c r="T72">
-        <v>2.677318595843678</v>
+        <v>2.761650580792335</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.579595170939324</v>
+        <v>1.55734735163032</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1200266588405294</v>
+        <v>0.1200843444947998</v>
       </c>
       <c r="C73">
-        <v>50.86812584620574</v>
+        <v>48.30509314135966</v>
       </c>
       <c r="D73">
-        <v>206.0811258462057</v>
+        <v>205.9210931413596</v>
       </c>
       <c r="E73">
-        <v>45.413</v>
+        <v>47.81599999999999</v>
       </c>
       <c r="F73">
-        <v>170.613</v>
+        <v>173.016</v>
       </c>
       <c r="G73">
         <v>15.4</v>
@@ -7273,28 +7273,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M73">
-        <v>15.35517</v>
+        <v>15.57144</v>
       </c>
       <c r="N73">
-        <v>8.558163333333335</v>
+        <v>8.341893333333335</v>
       </c>
       <c r="O73">
-        <v>2.0539592</v>
+        <v>2.0020544</v>
       </c>
       <c r="P73">
-        <v>6.504204133333334</v>
+        <v>6.339838933333334</v>
       </c>
       <c r="Q73">
-        <v>7.924204133333334</v>
+        <v>7.759838933333334</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2464229615190667</v>
+        <v>0.2529869446242848</v>
       </c>
       <c r="T73">
-        <v>2.761650580792335</v>
+        <v>2.85200627895161</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.55734735163032</v>
+        <v>1.535717527302121</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1200843444947998</v>
+        <v>0.1201420301490702</v>
       </c>
       <c r="C74">
-        <v>48.30509314135966</v>
+        <v>45.74230879107873</v>
       </c>
       <c r="D74">
-        <v>205.9210931413596</v>
+        <v>205.7613087910787</v>
       </c>
       <c r="E74">
-        <v>47.81599999999999</v>
+        <v>50.21900000000001</v>
       </c>
       <c r="F74">
-        <v>173.016</v>
+        <v>175.419</v>
       </c>
       <c r="G74">
         <v>15.4</v>
@@ -7355,28 +7355,28 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M74">
-        <v>15.57144</v>
+        <v>15.78771</v>
       </c>
       <c r="N74">
-        <v>8.341893333333335</v>
+        <v>8.125623333333333</v>
       </c>
       <c r="O74">
-        <v>2.0020544</v>
+        <v>1.9501496</v>
       </c>
       <c r="P74">
-        <v>6.339838933333334</v>
+        <v>6.175473733333334</v>
       </c>
       <c r="Q74">
-        <v>7.759838933333334</v>
+        <v>7.595473733333334</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2529869446242848</v>
+        <v>0.2600371487002598</v>
       </c>
       <c r="T74">
-        <v>2.85200627895161</v>
+        <v>2.94905499178935</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.535717527302121</v>
+        <v>1.514680300900722</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1201420301490702</v>
+        <v>0.1553776092705756</v>
       </c>
       <c r="C75">
-        <v>45.74230879107873</v>
+        <v>-22.82492790211415</v>
       </c>
       <c r="D75">
-        <v>205.7613087910787</v>
+        <v>139.5970720978858</v>
       </c>
       <c r="E75">
-        <v>50.21900000000001</v>
+        <v>52.622</v>
       </c>
       <c r="F75">
-        <v>175.419</v>
+        <v>177.822</v>
       </c>
       <c r="G75">
         <v>15.4</v>
@@ -7437,45 +7437,45 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M75">
-        <v>15.78771</v>
+        <v>26.1042696</v>
       </c>
       <c r="N75">
-        <v>8.125623333333333</v>
+        <v>-2.190936266666668</v>
       </c>
       <c r="O75">
-        <v>1.9501496</v>
+        <v>-0.5258247040000004</v>
       </c>
       <c r="P75">
-        <v>6.175473733333334</v>
+        <v>-1.665111562666668</v>
       </c>
       <c r="Q75">
-        <v>7.595473733333334</v>
+        <v>-0.2451115626666678</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2600371487002598</v>
+        <v>0.2716503394429932</v>
       </c>
       <c r="T75">
-        <v>2.94905499178935</v>
+        <v>3.108914933625936</v>
       </c>
       <c r="U75">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.24</v>
+        <v>0.2198567547739393</v>
       </c>
       <c r="W75">
-        <v>0.0684</v>
+        <v>0.1145250283991857</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y75">
-        <v>1.514680300900722</v>
+        <v>0.9160698115580806</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1553776092705756</v>
+        <v>0.1563876092705757</v>
       </c>
       <c r="C76">
-        <v>-22.82492790211415</v>
+        <v>-26.50287220870371</v>
       </c>
       <c r="D76">
-        <v>139.5970720978858</v>
+        <v>138.3221277912963</v>
       </c>
       <c r="E76">
-        <v>52.622</v>
+        <v>55.02500000000002</v>
       </c>
       <c r="F76">
-        <v>177.822</v>
+        <v>180.225</v>
       </c>
       <c r="G76">
         <v>15.4</v>
@@ -7519,37 +7519,37 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M76">
-        <v>26.1042696</v>
+        <v>26.45703000000001</v>
       </c>
       <c r="N76">
-        <v>-2.190936266666668</v>
+        <v>-2.543696666666673</v>
       </c>
       <c r="O76">
-        <v>-0.5258247040000004</v>
+        <v>-0.6104872000000015</v>
       </c>
       <c r="P76">
-        <v>-1.665111562666668</v>
+        <v>-1.933209466666671</v>
       </c>
       <c r="Q76">
-        <v>-0.2451115626666678</v>
+        <v>-0.5132094666666713</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2716503394429932</v>
+        <v>0.2806843530207129</v>
       </c>
       <c r="T76">
-        <v>3.108914933625936</v>
+        <v>3.233271530970974</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.2198567547739393</v>
+        <v>0.2169253313769534</v>
       </c>
       <c r="W76">
-        <v>0.1145250283991857</v>
+        <v>0.1149553613538632</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.9160698115580806</v>
+        <v>0.9038555474039727</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1563876092705757</v>
+        <v>0.1573976092705757</v>
       </c>
       <c r="C77">
-        <v>-26.50287220870371</v>
+        <v>-30.15773907200261</v>
       </c>
       <c r="D77">
-        <v>138.3221277912963</v>
+        <v>137.0702609279974</v>
       </c>
       <c r="E77">
-        <v>55.02500000000002</v>
+        <v>57.42800000000001</v>
       </c>
       <c r="F77">
-        <v>180.225</v>
+        <v>182.628</v>
       </c>
       <c r="G77">
         <v>15.4</v>
@@ -7601,37 +7601,37 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M77">
-        <v>26.45703000000001</v>
+        <v>26.8097904</v>
       </c>
       <c r="N77">
-        <v>-2.543696666666673</v>
+        <v>-2.89645706666667</v>
       </c>
       <c r="O77">
-        <v>-0.6104872000000015</v>
+        <v>-0.6951496960000009</v>
       </c>
       <c r="P77">
-        <v>-1.933209466666671</v>
+        <v>-2.201307370666669</v>
       </c>
       <c r="Q77">
-        <v>-0.5132094666666713</v>
+        <v>-0.7813073706666693</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2806843530207129</v>
+        <v>0.2904712010632427</v>
       </c>
       <c r="T77">
-        <v>3.233271530970974</v>
+        <v>3.367991178094765</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.2169253313769534</v>
+        <v>0.2140710507009409</v>
       </c>
       <c r="W77">
-        <v>0.1149553613538632</v>
+        <v>0.1153743697571019</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.9038555474039727</v>
+        <v>0.8919627112539206</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1573976092705757</v>
+        <v>0.1584076092705757</v>
       </c>
       <c r="C78">
-        <v>-30.15773907200261</v>
+        <v>-33.79014945052</v>
       </c>
       <c r="D78">
-        <v>137.0702609279974</v>
+        <v>135.84085054948</v>
       </c>
       <c r="E78">
-        <v>57.42800000000001</v>
+        <v>59.831</v>
       </c>
       <c r="F78">
-        <v>182.628</v>
+        <v>185.031</v>
       </c>
       <c r="G78">
         <v>15.4</v>
@@ -7683,37 +7683,37 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M78">
-        <v>26.8097904</v>
+        <v>27.1625508</v>
       </c>
       <c r="N78">
-        <v>-2.89645706666667</v>
+        <v>-3.249217466666668</v>
       </c>
       <c r="O78">
-        <v>-0.6951496960000009</v>
+        <v>-0.7798121920000003</v>
       </c>
       <c r="P78">
-        <v>-2.201307370666669</v>
+        <v>-2.469405274666667</v>
       </c>
       <c r="Q78">
-        <v>-0.7813073706666693</v>
+        <v>-1.049405274666667</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2904712010632427</v>
+        <v>0.3011090793703402</v>
       </c>
       <c r="T78">
-        <v>3.367991178094765</v>
+        <v>3.514425577142363</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.2140710507009409</v>
+        <v>0.2112909071853443</v>
       </c>
       <c r="W78">
-        <v>0.1153743697571019</v>
+        <v>0.1157824948251915</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8919627112539206</v>
+        <v>0.8803787799389347</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1584076092705757</v>
+        <v>0.1594176092705757</v>
       </c>
       <c r="C79">
-        <v>-33.79014945052</v>
+        <v>-37.40070222280411</v>
       </c>
       <c r="D79">
-        <v>135.84085054948</v>
+        <v>134.6332977771959</v>
       </c>
       <c r="E79">
-        <v>59.831</v>
+        <v>62.23400000000002</v>
       </c>
       <c r="F79">
-        <v>185.031</v>
+        <v>187.434</v>
       </c>
       <c r="G79">
         <v>15.4</v>
@@ -7765,37 +7765,37 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M79">
-        <v>27.1625508</v>
+        <v>27.51531120000001</v>
       </c>
       <c r="N79">
-        <v>-3.249217466666668</v>
+        <v>-3.601977866666672</v>
       </c>
       <c r="O79">
-        <v>-0.7798121920000003</v>
+        <v>-0.8644746880000014</v>
       </c>
       <c r="P79">
-        <v>-2.469405274666667</v>
+        <v>-2.737503178666671</v>
       </c>
       <c r="Q79">
-        <v>-1.049405274666667</v>
+        <v>-1.317503178666671</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3011090793703402</v>
+        <v>0.3127140375235375</v>
       </c>
       <c r="T79">
-        <v>3.514425577142363</v>
+        <v>3.674172194285199</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.2112909071853443</v>
+        <v>0.2085820494009168</v>
       </c>
       <c r="W79">
-        <v>0.1157824948251915</v>
+        <v>0.1161801551479454</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8803787799389347</v>
+        <v>0.8690918725038199</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1594176092705757</v>
+        <v>0.1604276092705757</v>
       </c>
       <c r="C80">
-        <v>-37.40070222280411</v>
+        <v>-40.98997516019037</v>
       </c>
       <c r="D80">
-        <v>134.6332977771959</v>
+        <v>133.4470248398096</v>
       </c>
       <c r="E80">
-        <v>62.23400000000002</v>
+        <v>64.63700000000001</v>
       </c>
       <c r="F80">
-        <v>187.434</v>
+        <v>189.837</v>
       </c>
       <c r="G80">
         <v>15.4</v>
@@ -7847,37 +7847,37 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M80">
-        <v>27.51531120000001</v>
+        <v>27.8680716</v>
       </c>
       <c r="N80">
-        <v>-3.601977866666672</v>
+        <v>-3.95473826666667</v>
       </c>
       <c r="O80">
-        <v>-0.8644746880000014</v>
+        <v>-0.9491371840000008</v>
       </c>
       <c r="P80">
-        <v>-2.737503178666671</v>
+        <v>-3.005601082666669</v>
       </c>
       <c r="Q80">
-        <v>-1.317503178666671</v>
+        <v>-1.585601082666669</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3127140375235375</v>
+        <v>0.3254242297865631</v>
       </c>
       <c r="T80">
-        <v>3.674172194285199</v>
+        <v>3.849132774965446</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.2085820494009168</v>
+        <v>0.2059417702945761</v>
       </c>
       <c r="W80">
-        <v>0.1161801551479454</v>
+        <v>0.1165677481207563</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8690918725038199</v>
+        <v>0.8580907095607337</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1604276092705757</v>
+        <v>0.1614376092705757</v>
       </c>
       <c r="C81">
-        <v>-40.98997516019037</v>
+        <v>-44.55852584857271</v>
       </c>
       <c r="D81">
-        <v>133.4470248398096</v>
+        <v>132.2814741514273</v>
       </c>
       <c r="E81">
-        <v>64.63700000000001</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="F81">
-        <v>189.837</v>
+        <v>192.24</v>
       </c>
       <c r="G81">
         <v>15.4</v>
@@ -7929,37 +7929,37 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M81">
-        <v>27.8680716</v>
+        <v>28.22083200000001</v>
       </c>
       <c r="N81">
-        <v>-3.95473826666667</v>
+        <v>-4.307498666666671</v>
       </c>
       <c r="O81">
-        <v>-0.9491371840000008</v>
+        <v>-1.033799680000001</v>
       </c>
       <c r="P81">
-        <v>-3.005601082666669</v>
+        <v>-3.27369898666667</v>
       </c>
       <c r="Q81">
-        <v>-1.585601082666669</v>
+        <v>-1.85369898666667</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3254242297865631</v>
+        <v>0.3394054412758913</v>
       </c>
       <c r="T81">
-        <v>3.849132774965446</v>
+        <v>4.041589413713719</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.2059417702945761</v>
+        <v>0.2033674981658939</v>
       </c>
       <c r="W81">
-        <v>0.1165677481207563</v>
+        <v>0.1169456512692468</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8580907095607337</v>
+        <v>0.8473645756912245</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1614376092705757</v>
+        <v>0.1624476092705757</v>
       </c>
       <c r="C82">
-        <v>-44.55852584857271</v>
+        <v>-48.10689256228761</v>
       </c>
       <c r="D82">
-        <v>132.2814741514273</v>
+        <v>131.1361074377124</v>
       </c>
       <c r="E82">
-        <v>67.04000000000001</v>
+        <v>69.44300000000003</v>
       </c>
       <c r="F82">
-        <v>192.24</v>
+        <v>194.643</v>
       </c>
       <c r="G82">
         <v>15.4</v>
@@ -8011,37 +8011,37 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M82">
-        <v>28.22083200000001</v>
+        <v>28.57359240000001</v>
       </c>
       <c r="N82">
-        <v>-4.307498666666671</v>
+        <v>-4.660259066666672</v>
       </c>
       <c r="O82">
-        <v>-1.033799680000001</v>
+        <v>-1.118462176000001</v>
       </c>
       <c r="P82">
-        <v>-3.27369898666667</v>
+        <v>-3.541796890666671</v>
       </c>
       <c r="Q82">
-        <v>-1.85369898666667</v>
+        <v>-2.121796890666671</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3394054412758913</v>
+        <v>0.3548583592377803</v>
       </c>
       <c r="T82">
-        <v>4.041589413713719</v>
+        <v>4.25430464601444</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.2033674981658939</v>
+        <v>0.2008567883119939</v>
       </c>
       <c r="W82">
-        <v>0.1169456512692468</v>
+        <v>0.1173142234757993</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8473645756912245</v>
+        <v>0.8369032846333081</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1624476092705757</v>
+        <v>0.1634576092705757</v>
       </c>
       <c r="C83">
-        <v>-48.10689256228761</v>
+        <v>-51.63559509298841</v>
       </c>
       <c r="D83">
-        <v>131.1361074377124</v>
+        <v>130.0104049070116</v>
       </c>
       <c r="E83">
-        <v>69.44300000000003</v>
+        <v>71.84600000000002</v>
       </c>
       <c r="F83">
-        <v>194.643</v>
+        <v>197.046</v>
       </c>
       <c r="G83">
         <v>15.4</v>
@@ -8093,37 +8093,37 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M83">
-        <v>28.57359240000001</v>
+        <v>28.92635280000001</v>
       </c>
       <c r="N83">
-        <v>-4.660259066666672</v>
+        <v>-5.013019466666673</v>
       </c>
       <c r="O83">
-        <v>-1.118462176000001</v>
+        <v>-1.203124672000002</v>
       </c>
       <c r="P83">
-        <v>-3.541796890666671</v>
+        <v>-3.809894794666672</v>
       </c>
       <c r="Q83">
-        <v>-2.121796890666671</v>
+        <v>-2.389894794666672</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3548583592377803</v>
+        <v>0.3720282680843237</v>
       </c>
       <c r="T83">
-        <v>4.25430464601444</v>
+        <v>4.490654904126354</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.2008567883119939</v>
+        <v>0.1984073152837989</v>
       </c>
       <c r="W83">
-        <v>0.1173142234757993</v>
+        <v>0.1176738061163383</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8369032846333081</v>
+        <v>0.8266971470158286</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1634576092705757</v>
+        <v>0.1644676092705757</v>
       </c>
       <c r="C84">
-        <v>-51.63559509298841</v>
+        <v>-55.14513553619125</v>
       </c>
       <c r="D84">
-        <v>130.0104049070116</v>
+        <v>128.9038644638088</v>
       </c>
       <c r="E84">
-        <v>71.84600000000002</v>
+        <v>74.24900000000004</v>
       </c>
       <c r="F84">
-        <v>197.046</v>
+        <v>199.449</v>
       </c>
       <c r="G84">
         <v>15.4</v>
@@ -8175,37 +8175,37 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M84">
-        <v>28.92635280000001</v>
+        <v>29.27911320000001</v>
       </c>
       <c r="N84">
-        <v>-5.013019466666673</v>
+        <v>-5.365779866666674</v>
       </c>
       <c r="O84">
-        <v>-1.203124672000002</v>
+        <v>-1.287787168000002</v>
       </c>
       <c r="P84">
-        <v>-3.809894794666672</v>
+        <v>-4.077992698666673</v>
       </c>
       <c r="Q84">
-        <v>-2.389894794666672</v>
+        <v>-2.657992698666673</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3720282680843237</v>
+        <v>0.391218166206931</v>
       </c>
       <c r="T84">
-        <v>4.490654904126354</v>
+        <v>4.754811074957317</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.1984073152837989</v>
+        <v>0.1960168657020664</v>
       </c>
       <c r="W84">
-        <v>0.1176738061163383</v>
+        <v>0.1180247241149367</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8266971470158286</v>
+        <v>0.8167369404252764</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1644676092705757</v>
+        <v>0.1654776092705757</v>
       </c>
       <c r="C85">
-        <v>-55.14513553619125</v>
+        <v>-58.6359990379938</v>
       </c>
       <c r="D85">
-        <v>128.9038644638088</v>
+        <v>127.8160009620062</v>
       </c>
       <c r="E85">
-        <v>74.24900000000004</v>
+        <v>76.65200000000003</v>
       </c>
       <c r="F85">
-        <v>199.449</v>
+        <v>201.852</v>
       </c>
       <c r="G85">
         <v>15.4</v>
@@ -8257,37 +8257,37 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M85">
-        <v>29.27911320000001</v>
+        <v>29.63187360000001</v>
       </c>
       <c r="N85">
-        <v>-5.365779866666674</v>
+        <v>-5.718540266666672</v>
       </c>
       <c r="O85">
-        <v>-1.287787168000002</v>
+        <v>-1.372449664000001</v>
       </c>
       <c r="P85">
-        <v>-4.077992698666673</v>
+        <v>-4.346090602666671</v>
       </c>
       <c r="Q85">
-        <v>-2.657992698666673</v>
+        <v>-2.926090602666671</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.391218166206931</v>
+        <v>0.4128068015948642</v>
       </c>
       <c r="T85">
-        <v>4.754811074957317</v>
+        <v>5.05198676714215</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.1960168657020664</v>
+        <v>0.1936833315865656</v>
       </c>
       <c r="W85">
-        <v>0.1180247241149367</v>
+        <v>0.1183672869230922</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8167369404252764</v>
+        <v>0.80701388161069</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1654776092705757</v>
+        <v>0.2154560057503377</v>
       </c>
       <c r="C86">
-        <v>-58.63599903799377</v>
+        <v>-98.69188815491249</v>
       </c>
       <c r="D86">
-        <v>127.8160009620062</v>
+        <v>90.1631118450875</v>
       </c>
       <c r="E86">
-        <v>76.652</v>
+        <v>79.05499999999999</v>
       </c>
       <c r="F86">
-        <v>201.852</v>
+        <v>204.255</v>
       </c>
       <c r="G86">
         <v>15.4</v>
@@ -8339,45 +8339,45 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M86">
-        <v>29.6318736</v>
+        <v>41.014404</v>
       </c>
       <c r="N86">
-        <v>-5.718540266666668</v>
+        <v>-17.10107066666666</v>
       </c>
       <c r="O86">
-        <v>-1.372449664</v>
+        <v>-4.10425696</v>
       </c>
       <c r="P86">
-        <v>-4.346090602666668</v>
+        <v>-12.99681370666666</v>
       </c>
       <c r="Q86">
-        <v>-2.926090602666668</v>
+        <v>-11.57681370666666</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.412806801594864</v>
+        <v>0.4577298982329352</v>
       </c>
       <c r="T86">
-        <v>5.051986767142147</v>
+        <v>5.670370101642614</v>
       </c>
       <c r="U86">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1936833315865656</v>
+        <v>0.1399313275404417</v>
       </c>
       <c r="W86">
-        <v>0.1183672869230922</v>
+        <v>0.1727017894298793</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.8070138816106901</v>
+        <v>0.5830471980851736</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2154560057503377</v>
+        <v>0.2170060057503377</v>
       </c>
       <c r="C87">
-        <v>-98.69188815491249</v>
+        <v>-101.9111727399503</v>
       </c>
       <c r="D87">
-        <v>90.1631118450875</v>
+        <v>89.34682726004974</v>
       </c>
       <c r="E87">
-        <v>79.05499999999999</v>
+        <v>81.45800000000001</v>
       </c>
       <c r="F87">
-        <v>204.255</v>
+        <v>206.658</v>
       </c>
       <c r="G87">
         <v>15.4</v>
@@ -8421,37 +8421,37 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M87">
-        <v>41.014404</v>
+        <v>41.49692640000001</v>
       </c>
       <c r="N87">
-        <v>-17.10107066666666</v>
+        <v>-17.58359306666667</v>
       </c>
       <c r="O87">
-        <v>-4.10425696</v>
+        <v>-4.220062336000002</v>
       </c>
       <c r="P87">
-        <v>-12.99681370666666</v>
+        <v>-13.36353073066667</v>
       </c>
       <c r="Q87">
-        <v>-11.57681370666666</v>
+        <v>-11.94353073066667</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4577298982329352</v>
+        <v>0.4871534623924306</v>
       </c>
       <c r="T87">
-        <v>5.670370101642614</v>
+        <v>6.075396537474231</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1399313275404417</v>
+        <v>0.1383042190806691</v>
       </c>
       <c r="W87">
-        <v>0.1727017894298793</v>
+        <v>0.1730285128086017</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5830471980851736</v>
+        <v>0.5762675795027877</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2170060057503377</v>
+        <v>0.2185560057503377</v>
       </c>
       <c r="C88">
-        <v>-101.9111727399503</v>
+        <v>-105.1158096014393</v>
       </c>
       <c r="D88">
-        <v>89.34682726004974</v>
+        <v>88.54519039856075</v>
       </c>
       <c r="E88">
-        <v>81.45800000000001</v>
+        <v>83.861</v>
       </c>
       <c r="F88">
-        <v>206.658</v>
+        <v>209.061</v>
       </c>
       <c r="G88">
         <v>15.4</v>
@@ -8503,37 +8503,37 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M88">
-        <v>41.49692640000001</v>
+        <v>41.9794488</v>
       </c>
       <c r="N88">
-        <v>-17.58359306666667</v>
+        <v>-18.06611546666667</v>
       </c>
       <c r="O88">
-        <v>-4.220062336000002</v>
+        <v>-4.335867712</v>
       </c>
       <c r="P88">
-        <v>-13.36353073066667</v>
+        <v>-13.73024775466667</v>
       </c>
       <c r="Q88">
-        <v>-11.94353073066667</v>
+        <v>-12.31024775466667</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4871534623924306</v>
+        <v>0.52110372873031</v>
       </c>
       <c r="T88">
-        <v>6.075396537474231</v>
+        <v>6.542734732664557</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1383042190806691</v>
+        <v>0.1367145154130752</v>
       </c>
       <c r="W88">
-        <v>0.1730285128086017</v>
+        <v>0.1733477253050545</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5762675795027877</v>
+        <v>0.5696438142211466</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2185560057503377</v>
+        <v>0.2201060057503377</v>
       </c>
       <c r="C89">
-        <v>-105.1158096014393</v>
+        <v>-108.3061894999514</v>
       </c>
       <c r="D89">
-        <v>88.54519039856075</v>
+        <v>87.75781050004855</v>
       </c>
       <c r="E89">
-        <v>83.861</v>
+        <v>86.264</v>
       </c>
       <c r="F89">
-        <v>209.061</v>
+        <v>211.464</v>
       </c>
       <c r="G89">
         <v>15.4</v>
@@ -8585,37 +8585,37 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M89">
-        <v>41.9794488</v>
+        <v>42.4619712</v>
       </c>
       <c r="N89">
-        <v>-18.06611546666667</v>
+        <v>-18.54863786666667</v>
       </c>
       <c r="O89">
-        <v>-4.335867712</v>
+        <v>-4.451673088</v>
       </c>
       <c r="P89">
-        <v>-13.73024775466667</v>
+        <v>-14.09696477866667</v>
       </c>
       <c r="Q89">
-        <v>-12.31024775466667</v>
+        <v>-12.67696477866667</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.52110372873031</v>
+        <v>0.560712372791169</v>
       </c>
       <c r="T89">
-        <v>6.542734732664557</v>
+        <v>7.08796262705327</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1367145154130752</v>
+        <v>0.1351609413742902</v>
       </c>
       <c r="W89">
-        <v>0.1733477253050545</v>
+        <v>0.1736596829720425</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5696438142211466</v>
+        <v>0.5631705890595426</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2201060057503377</v>
+        <v>0.2216560057503377</v>
       </c>
       <c r="C90">
-        <v>-108.3061894999514</v>
+        <v>-111.4826894193582</v>
       </c>
       <c r="D90">
-        <v>87.75781050004855</v>
+        <v>86.98431058064182</v>
       </c>
       <c r="E90">
-        <v>86.264</v>
+        <v>88.66700000000002</v>
       </c>
       <c r="F90">
-        <v>211.464</v>
+        <v>213.867</v>
       </c>
       <c r="G90">
         <v>15.4</v>
@@ -8667,37 +8667,37 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M90">
-        <v>42.4619712</v>
+        <v>42.94449360000001</v>
       </c>
       <c r="N90">
-        <v>-18.54863786666667</v>
+        <v>-19.03116026666667</v>
       </c>
       <c r="O90">
-        <v>-4.451673088</v>
+        <v>-4.567478464000001</v>
       </c>
       <c r="P90">
-        <v>-14.09696477866667</v>
+        <v>-14.46368180266667</v>
       </c>
       <c r="Q90">
-        <v>-12.67696477866667</v>
+        <v>-13.04368180266667</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.560712372791169</v>
+        <v>0.6075225884994572</v>
       </c>
       <c r="T90">
-        <v>7.08796262705327</v>
+        <v>7.732322865876295</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1351609413742902</v>
+        <v>0.1336422791116577</v>
       </c>
       <c r="W90">
-        <v>0.1736596829720425</v>
+        <v>0.1739646303543791</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5631705890595426</v>
+        <v>0.5568428296319072</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2216560057503377</v>
+        <v>0.2232060057503377</v>
       </c>
       <c r="C91">
-        <v>-111.4826894193582</v>
+        <v>-114.6456731686667</v>
       </c>
       <c r="D91">
-        <v>86.98431058064182</v>
+        <v>86.22432683133326</v>
       </c>
       <c r="E91">
-        <v>88.66700000000002</v>
+        <v>91.07000000000001</v>
       </c>
       <c r="F91">
-        <v>213.867</v>
+        <v>216.27</v>
       </c>
       <c r="G91">
         <v>15.4</v>
@@ -8749,37 +8749,37 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M91">
-        <v>42.94449360000001</v>
+        <v>43.427016</v>
       </c>
       <c r="N91">
-        <v>-19.03116026666667</v>
+        <v>-19.51368266666667</v>
       </c>
       <c r="O91">
-        <v>-4.567478464000001</v>
+        <v>-4.683283840000001</v>
       </c>
       <c r="P91">
-        <v>-14.46368180266667</v>
+        <v>-14.83039882666667</v>
       </c>
       <c r="Q91">
-        <v>-13.04368180266667</v>
+        <v>-13.41039882666667</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6075225884994572</v>
+        <v>0.663694847349403</v>
       </c>
       <c r="T91">
-        <v>7.732322865876295</v>
+        <v>8.505555152463925</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1336422791116577</v>
+        <v>0.132157364899306</v>
       </c>
       <c r="W91">
-        <v>0.1739646303543791</v>
+        <v>0.1742628011282194</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5568428296319072</v>
+        <v>0.5506556870804417</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2232060057503377</v>
+        <v>0.2247560057503377</v>
       </c>
       <c r="C92">
-        <v>-114.6456731686667</v>
+        <v>-117.7954919525807</v>
       </c>
       <c r="D92">
-        <v>86.22432683133326</v>
+        <v>85.47750804741931</v>
       </c>
       <c r="E92">
-        <v>91.07000000000001</v>
+        <v>93.47300000000003</v>
       </c>
       <c r="F92">
-        <v>216.27</v>
+        <v>218.673</v>
       </c>
       <c r="G92">
         <v>15.4</v>
@@ -8831,37 +8831,37 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M92">
-        <v>43.427016</v>
+        <v>43.90953840000001</v>
       </c>
       <c r="N92">
-        <v>-19.51368266666667</v>
+        <v>-19.99620506666668</v>
       </c>
       <c r="O92">
-        <v>-4.683283840000001</v>
+        <v>-4.799089216000002</v>
       </c>
       <c r="P92">
-        <v>-14.83039882666667</v>
+        <v>-15.19711585066667</v>
       </c>
       <c r="Q92">
-        <v>-13.41039882666667</v>
+        <v>-13.77711585066667</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.663694847349403</v>
+        <v>0.7323498303882255</v>
       </c>
       <c r="T92">
-        <v>8.505555152463925</v>
+        <v>9.450616836071028</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.132157364899306</v>
+        <v>0.1307050861641488</v>
       </c>
       <c r="W92">
-        <v>0.1742628011282194</v>
+        <v>0.1745544186982389</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5506556870804417</v>
+        <v>0.5446045256839531</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2247560057503377</v>
+        <v>0.2263060057503377</v>
       </c>
       <c r="C93">
-        <v>-117.7954919525807</v>
+        <v>-120.932484912664</v>
       </c>
       <c r="D93">
-        <v>85.47750804741931</v>
+        <v>84.74351508733604</v>
       </c>
       <c r="E93">
-        <v>93.47300000000003</v>
+        <v>95.87600000000002</v>
       </c>
       <c r="F93">
-        <v>218.673</v>
+        <v>221.076</v>
       </c>
       <c r="G93">
         <v>15.4</v>
@@ -8913,37 +8913,37 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M93">
-        <v>43.90953840000001</v>
+        <v>44.3920608</v>
       </c>
       <c r="N93">
-        <v>-19.99620506666668</v>
+        <v>-20.47872746666667</v>
       </c>
       <c r="O93">
-        <v>-4.799089216000002</v>
+        <v>-4.914894592</v>
       </c>
       <c r="P93">
-        <v>-15.19711585066667</v>
+        <v>-15.56383287466667</v>
       </c>
       <c r="Q93">
-        <v>-13.77711585066667</v>
+        <v>-14.14383287466667</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7323498303882255</v>
+        <v>0.8181685591867539</v>
       </c>
       <c r="T93">
-        <v>9.450616836071028</v>
+        <v>10.63194394057991</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1307050861641488</v>
+        <v>0.1292843787058428</v>
       </c>
       <c r="W93">
-        <v>0.1745544186982389</v>
+        <v>0.1748396967558667</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5446045256839531</v>
+        <v>0.538684911274345</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2263060057503377</v>
+        <v>0.2278560057503377</v>
       </c>
       <c r="C94">
-        <v>-120.932484912664</v>
+        <v>-124.0569796408604</v>
       </c>
       <c r="D94">
-        <v>84.74351508733604</v>
+        <v>84.0220203591396</v>
       </c>
       <c r="E94">
-        <v>95.87600000000002</v>
+        <v>98.27900000000001</v>
       </c>
       <c r="F94">
-        <v>221.076</v>
+        <v>223.479</v>
       </c>
       <c r="G94">
         <v>15.4</v>
@@ -8995,37 +8995,37 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M94">
-        <v>44.3920608</v>
+        <v>44.8745832</v>
       </c>
       <c r="N94">
-        <v>-20.47872746666667</v>
+        <v>-20.96124986666667</v>
       </c>
       <c r="O94">
-        <v>-4.914894592</v>
+        <v>-5.030699968</v>
       </c>
       <c r="P94">
-        <v>-15.56383287466667</v>
+        <v>-15.93054989866667</v>
       </c>
       <c r="Q94">
-        <v>-14.14383287466667</v>
+        <v>-14.51054989866667</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8181685591867539</v>
+        <v>0.9285069247848619</v>
       </c>
       <c r="T94">
-        <v>10.63194394057991</v>
+        <v>12.15079307494847</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1292843787058428</v>
+        <v>0.1278942240961026</v>
       </c>
       <c r="W94">
-        <v>0.1748396967558667</v>
+        <v>0.1751188398015026</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.538684911274345</v>
+        <v>0.5328926004004274</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2278560057503377</v>
+        <v>0.2294060057503377</v>
       </c>
       <c r="C95">
-        <v>-124.0569796408604</v>
+        <v>-127.1692926670027</v>
       </c>
       <c r="D95">
-        <v>84.0220203591396</v>
+        <v>83.31270733299731</v>
       </c>
       <c r="E95">
-        <v>98.27900000000001</v>
+        <v>100.682</v>
       </c>
       <c r="F95">
-        <v>223.479</v>
+        <v>225.882</v>
       </c>
       <c r="G95">
         <v>15.4</v>
@@ -9077,37 +9077,37 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M95">
-        <v>44.8745832</v>
+        <v>45.35710560000001</v>
       </c>
       <c r="N95">
-        <v>-20.96124986666667</v>
+        <v>-21.44377226666668</v>
       </c>
       <c r="O95">
-        <v>-5.030699968</v>
+        <v>-5.146505344000002</v>
       </c>
       <c r="P95">
-        <v>-15.93054989866667</v>
+        <v>-16.29726692266668</v>
       </c>
       <c r="Q95">
-        <v>-14.51054989866667</v>
+        <v>-14.87726692266668</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9285069247848619</v>
+        <v>1.075624745582339</v>
       </c>
       <c r="T95">
-        <v>12.15079307494847</v>
+        <v>14.17592525410655</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1278942240961026</v>
+        <v>0.1265336472440164</v>
       </c>
       <c r="W95">
-        <v>0.1751188398015026</v>
+        <v>0.1753920436334015</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5328926004004274</v>
+        <v>0.5272235301834014</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2294060057503377</v>
+        <v>0.2309560057503377</v>
       </c>
       <c r="C96">
-        <v>-127.1692926670027</v>
+        <v>-130.2697299218345</v>
       </c>
       <c r="D96">
-        <v>83.31270733299731</v>
+        <v>82.61527007816547</v>
       </c>
       <c r="E96">
-        <v>100.682</v>
+        <v>103.085</v>
       </c>
       <c r="F96">
-        <v>225.882</v>
+        <v>228.285</v>
       </c>
       <c r="G96">
         <v>15.4</v>
@@ -9159,37 +9159,37 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M96">
-        <v>45.35710560000001</v>
+        <v>45.839628</v>
       </c>
       <c r="N96">
-        <v>-21.44377226666668</v>
+        <v>-21.92629466666667</v>
       </c>
       <c r="O96">
-        <v>-5.146505344000002</v>
+        <v>-5.262310720000001</v>
       </c>
       <c r="P96">
-        <v>-16.29726692266668</v>
+        <v>-16.66398394666667</v>
       </c>
       <c r="Q96">
-        <v>-14.87726692266668</v>
+        <v>-15.24398394666667</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.075624745582339</v>
+        <v>1.281589694698808</v>
       </c>
       <c r="T96">
-        <v>14.17592525410655</v>
+        <v>17.01111030492787</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1265336472440164</v>
+        <v>0.125201714115132</v>
       </c>
       <c r="W96">
-        <v>0.1753920436334015</v>
+        <v>0.1756594958056815</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5272235301834014</v>
+        <v>0.5216738088130499</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2309560057503377</v>
+        <v>0.2325060057503377</v>
       </c>
       <c r="C97">
-        <v>-130.2697299218345</v>
+        <v>-133.3585871769696</v>
       </c>
       <c r="D97">
-        <v>82.61527007816547</v>
+        <v>81.9294128230304</v>
       </c>
       <c r="E97">
-        <v>103.085</v>
+        <v>105.488</v>
       </c>
       <c r="F97">
-        <v>228.285</v>
+        <v>230.688</v>
       </c>
       <c r="G97">
         <v>15.4</v>
@@ -9241,37 +9241,37 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M97">
-        <v>45.839628</v>
+        <v>46.32215040000001</v>
       </c>
       <c r="N97">
-        <v>-21.92629466666667</v>
+        <v>-22.40881706666667</v>
       </c>
       <c r="O97">
-        <v>-5.262310720000001</v>
+        <v>-5.378116096000001</v>
       </c>
       <c r="P97">
-        <v>-16.66398394666667</v>
+        <v>-17.03070097066667</v>
       </c>
       <c r="Q97">
-        <v>-15.24398394666667</v>
+        <v>-15.61070097066667</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.281589694698808</v>
+        <v>1.59053711837351</v>
       </c>
       <c r="T97">
-        <v>17.01111030492787</v>
+        <v>21.26388788115985</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.125201714115132</v>
+        <v>0.1238975295930994</v>
       </c>
       <c r="W97">
-        <v>0.1756594958056815</v>
+        <v>0.1759213760577057</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5216738088130499</v>
+        <v>0.5162397066379141</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2325060057503377</v>
+        <v>0.2340560057503377</v>
       </c>
       <c r="C98">
-        <v>-133.3585871769696</v>
+        <v>-136.4361504631157</v>
       </c>
       <c r="D98">
-        <v>81.92941282303042</v>
+        <v>81.25484953688428</v>
       </c>
       <c r="E98">
-        <v>105.488</v>
+        <v>107.891</v>
       </c>
       <c r="F98">
-        <v>230.688</v>
+        <v>233.091</v>
       </c>
       <c r="G98">
         <v>15.4</v>
@@ -9323,37 +9323,37 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M98">
-        <v>46.3221504</v>
+        <v>46.80467280000001</v>
       </c>
       <c r="N98">
-        <v>-22.40881706666666</v>
+        <v>-22.89133946666667</v>
       </c>
       <c r="O98">
-        <v>-5.378116095999999</v>
+        <v>-5.493921472000001</v>
       </c>
       <c r="P98">
-        <v>-17.03070097066666</v>
+        <v>-17.39741799466667</v>
       </c>
       <c r="Q98">
-        <v>-15.61070097066666</v>
+        <v>-15.97741799466667</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.590537118373506</v>
+        <v>2.105449491164674</v>
       </c>
       <c r="T98">
-        <v>21.26388788115979</v>
+        <v>28.35185050821305</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1238975295930994</v>
+        <v>0.1226202354735829</v>
       </c>
       <c r="W98">
-        <v>0.1759213760577056</v>
+        <v>0.1761778567169046</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5162397066379141</v>
+        <v>0.5109176478065953</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2340560057503377</v>
+        <v>0.2356060057503377</v>
       </c>
       <c r="C99">
-        <v>-136.4361504631157</v>
+        <v>-139.5026964678077</v>
       </c>
       <c r="D99">
-        <v>81.25484953688428</v>
+        <v>80.5913035321923</v>
       </c>
       <c r="E99">
-        <v>107.891</v>
+        <v>110.294</v>
       </c>
       <c r="F99">
-        <v>233.091</v>
+        <v>235.494</v>
       </c>
       <c r="G99">
         <v>15.4</v>
@@ -9405,37 +9405,37 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M99">
-        <v>46.80467280000001</v>
+        <v>47.2871952</v>
       </c>
       <c r="N99">
-        <v>-22.89133946666667</v>
+        <v>-23.37386186666667</v>
       </c>
       <c r="O99">
-        <v>-5.493921472000001</v>
+        <v>-5.609726847999999</v>
       </c>
       <c r="P99">
-        <v>-17.39741799466667</v>
+        <v>-17.76413501866666</v>
       </c>
       <c r="Q99">
-        <v>-15.97741799466667</v>
+        <v>-16.34413501866666</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.105449491164674</v>
+        <v>3.135274236747012</v>
       </c>
       <c r="T99">
-        <v>28.35185050821305</v>
+        <v>42.52777576231959</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1226202354735829</v>
+        <v>0.1213690085809953</v>
       </c>
       <c r="W99">
-        <v>0.1761778567169046</v>
+        <v>0.1764291030769362</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5109176478065953</v>
+        <v>0.5057042024208138</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2356060057503377</v>
+        <v>0.2371560057503377</v>
       </c>
       <c r="C100">
-        <v>-139.5026964678077</v>
+        <v>-142.5584929138094</v>
       </c>
       <c r="D100">
-        <v>80.5913035321923</v>
+        <v>79.93850708619064</v>
       </c>
       <c r="E100">
-        <v>110.294</v>
+        <v>112.697</v>
       </c>
       <c r="F100">
-        <v>235.494</v>
+        <v>237.897</v>
       </c>
       <c r="G100">
         <v>15.4</v>
@@ -9487,37 +9487,37 @@
         <v>23.91333333333333</v>
       </c>
       <c r="M100">
-        <v>47.2871952</v>
+        <v>47.76971760000001</v>
       </c>
       <c r="N100">
-        <v>-23.37386186666667</v>
+        <v>-23.85638426666667</v>
       </c>
       <c r="O100">
-        <v>-5.609726847999999</v>
+        <v>-5.725532224000001</v>
       </c>
       <c r="P100">
-        <v>-17.76413501866666</v>
+        <v>-18.13085204266667</v>
       </c>
       <c r="Q100">
-        <v>-16.34413501866666</v>
+        <v>-16.71085204266667</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.135274236747012</v>
+        <v>6.224748473494024</v>
       </c>
       <c r="T100">
-        <v>42.52777576231959</v>
+        <v>85.05555152463917</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1213690085809953</v>
+        <v>0.1201430589993691</v>
       </c>
       <c r="W100">
-        <v>0.1764291030769362</v>
+        <v>0.1766752737529267</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5057042024208138</v>
+        <v>0.5005960791640378</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2371560057503377</v>
-      </c>
-      <c r="C101">
-        <v>-142.5584929138094</v>
-      </c>
-      <c r="D101">
-        <v>79.93850708619064</v>
-      </c>
-      <c r="E101">
-        <v>112.697</v>
-      </c>
-      <c r="F101">
-        <v>237.897</v>
-      </c>
-      <c r="G101">
-        <v>15.4</v>
-      </c>
-      <c r="H101">
-        <v>115.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>25.33333333333333</v>
-      </c>
-      <c r="K101">
-        <v>1.42</v>
-      </c>
-      <c r="L101">
-        <v>23.91333333333333</v>
-      </c>
-      <c r="M101">
-        <v>47.76971760000001</v>
-      </c>
-      <c r="N101">
-        <v>-23.85638426666667</v>
-      </c>
-      <c r="O101">
-        <v>-5.725532224000001</v>
-      </c>
-      <c r="P101">
-        <v>-18.13085204266667</v>
-      </c>
-      <c r="Q101">
-        <v>-16.71085204266667</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.224748473494024</v>
-      </c>
-      <c r="T101">
-        <v>85.05555152463917</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1201430589993691</v>
-      </c>
-      <c r="W101">
-        <v>0.1766752737529267</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5005960791640378</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
